--- a/research/traditional_assets/database/data/poland/poland_diversified.xlsx
+++ b/research/traditional_assets/database/data/poland/poland_diversified.xlsx
@@ -1400,7 +1400,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1537,22 +1537,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.0855594189959992</v>
+        <v>0.08543330609990681</v>
       </c>
       <c r="C2">
-        <v>148.8087825835198</v>
+        <v>147.7887540119173</v>
       </c>
       <c r="D2">
-        <v>144.8687825835198</v>
+        <v>145.3297540119173</v>
       </c>
       <c r="E2">
-        <v>-114.7</v>
+        <v>-113.219</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.481</v>
       </c>
       <c r="G2">
         <v>3.94</v>
@@ -1573,28 +1573,28 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.07449429999999999</v>
       </c>
       <c r="N2">
-        <v>9.836666666666666</v>
+        <v>9.762172366666666</v>
       </c>
       <c r="O2">
-        <v>1.868966666666667</v>
+        <v>1.854812749666667</v>
       </c>
       <c r="P2">
-        <v>7.967699999999999</v>
+        <v>7.907359617</v>
       </c>
       <c r="Q2">
-        <v>11.9477</v>
+        <v>11.887359617</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.0855594189959992</v>
+        <v>0.0858847233332392</v>
       </c>
       <c r="T2">
-        <v>0.7282077218429368</v>
+        <v>0.7341657850216519</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>132.0458970238886</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1619,22 +1619,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08543330609990681</v>
+        <v>0.0853071932038144</v>
       </c>
       <c r="C3">
-        <v>147.7887540119173</v>
+        <v>146.7716684204223</v>
       </c>
       <c r="D3">
-        <v>145.3297540119173</v>
+        <v>145.7936684204223</v>
       </c>
       <c r="E3">
-        <v>-113.219</v>
+        <v>-111.738</v>
       </c>
       <c r="F3">
-        <v>1.481</v>
+        <v>2.962</v>
       </c>
       <c r="G3">
         <v>3.94</v>
@@ -1655,28 +1655,28 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M3">
-        <v>0.07449429999999999</v>
+        <v>0.1489886</v>
       </c>
       <c r="N3">
-        <v>9.762172366666666</v>
+        <v>9.687678066666667</v>
       </c>
       <c r="O3">
-        <v>1.854812749666667</v>
+        <v>1.840658832666667</v>
       </c>
       <c r="P3">
-        <v>7.907359617</v>
+        <v>7.847019234</v>
       </c>
       <c r="Q3">
-        <v>11.887359617</v>
+        <v>11.827019234</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.0858847233332392</v>
+        <v>0.08621666653450449</v>
       </c>
       <c r="T3">
-        <v>0.7341657850216519</v>
+        <v>0.740245441326463</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1693,7 +1693,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>132.0458970238886</v>
+        <v>66.02294851194434</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1701,22 +1701,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.0853071932038144</v>
+        <v>0.08518108030772201</v>
       </c>
       <c r="C4">
-        <v>146.7716684204223</v>
+        <v>145.757554082592</v>
       </c>
       <c r="D4">
-        <v>145.7936684204223</v>
+        <v>146.2605540825921</v>
       </c>
       <c r="E4">
-        <v>-111.738</v>
+        <v>-110.257</v>
       </c>
       <c r="F4">
-        <v>2.962</v>
+        <v>4.443</v>
       </c>
       <c r="G4">
         <v>3.94</v>
@@ -1737,28 +1737,28 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M4">
-        <v>0.1489886</v>
+        <v>0.2234829</v>
       </c>
       <c r="N4">
-        <v>9.687678066666667</v>
+        <v>9.613183766666666</v>
       </c>
       <c r="O4">
-        <v>1.840658832666667</v>
+        <v>1.826504915666666</v>
       </c>
       <c r="P4">
-        <v>7.847019234</v>
+        <v>7.786678851</v>
       </c>
       <c r="Q4">
-        <v>11.827019234</v>
+        <v>11.766678851</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08621666653450449</v>
+        <v>0.08655545392548661</v>
       </c>
       <c r="T4">
-        <v>0.740245441326463</v>
+        <v>0.7464504513695177</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>66.02294851194434</v>
+        <v>44.01529900796288</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1783,22 +1783,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08518108030772201</v>
+        <v>0.08505496741162959</v>
       </c>
       <c r="C5">
-        <v>145.757554082592</v>
+        <v>144.7464396353176</v>
       </c>
       <c r="D5">
-        <v>146.2605540825921</v>
+        <v>146.7304396353177</v>
       </c>
       <c r="E5">
-        <v>-110.257</v>
+        <v>-108.776</v>
       </c>
       <c r="F5">
-        <v>4.443</v>
+        <v>5.923999999999999</v>
       </c>
       <c r="G5">
         <v>3.94</v>
@@ -1819,28 +1819,28 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M5">
-        <v>0.2234829</v>
+        <v>0.2979771999999999</v>
       </c>
       <c r="N5">
-        <v>9.613183766666666</v>
+        <v>9.538689466666666</v>
       </c>
       <c r="O5">
-        <v>1.826504915666666</v>
+        <v>1.812350998666667</v>
       </c>
       <c r="P5">
-        <v>7.786678851</v>
+        <v>7.726338468</v>
       </c>
       <c r="Q5">
-        <v>11.766678851</v>
+        <v>11.706338468</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08655545392548661</v>
+        <v>0.08690129938711416</v>
       </c>
       <c r="T5">
-        <v>0.7464504513695177</v>
+        <v>0.7527847324551359</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1857,7 +1857,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>44.01529900796288</v>
+        <v>33.01147425597216</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1865,22 +1865,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08505496741162959</v>
+        <v>0.08492885451553719</v>
       </c>
       <c r="C6">
-        <v>144.7464396353176</v>
+        <v>143.7383540846781</v>
       </c>
       <c r="D6">
-        <v>146.7304396353177</v>
+        <v>147.2033540846781</v>
       </c>
       <c r="E6">
-        <v>-108.776</v>
+        <v>-107.295</v>
       </c>
       <c r="F6">
-        <v>5.923999999999999</v>
+        <v>7.405</v>
       </c>
       <c r="G6">
         <v>3.94</v>
@@ -1901,28 +1901,28 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M6">
-        <v>0.2979771999999999</v>
+        <v>0.3724715</v>
       </c>
       <c r="N6">
-        <v>9.538689466666666</v>
+        <v>9.464195166666666</v>
       </c>
       <c r="O6">
-        <v>1.812350998666667</v>
+        <v>1.798197081666667</v>
       </c>
       <c r="P6">
-        <v>7.726338468</v>
+        <v>7.665998085</v>
       </c>
       <c r="Q6">
-        <v>11.706338468</v>
+        <v>11.645998085</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08690129938711416</v>
+        <v>0.08725442580582862</v>
       </c>
       <c r="T6">
-        <v>0.7527847324551359</v>
+        <v>0.7592523668267672</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>33.01147425597216</v>
+        <v>26.40917940477772</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1947,22 +1947,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08492885451553719</v>
+        <v>0.08480274161944479</v>
       </c>
       <c r="C7">
-        <v>143.7383540846781</v>
+        <v>142.7333268119101</v>
       </c>
       <c r="D7">
-        <v>147.2033540846781</v>
+        <v>147.6793268119101</v>
       </c>
       <c r="E7">
-        <v>-107.295</v>
+        <v>-105.814</v>
       </c>
       <c r="F7">
-        <v>7.405</v>
+        <v>8.886000000000001</v>
       </c>
       <c r="G7">
         <v>3.94</v>
@@ -1983,28 +1983,28 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M7">
-        <v>0.3724715</v>
+        <v>0.4469658</v>
       </c>
       <c r="N7">
-        <v>9.464195166666666</v>
+        <v>9.389700866666667</v>
       </c>
       <c r="O7">
-        <v>1.798197081666667</v>
+        <v>1.784043164666667</v>
       </c>
       <c r="P7">
-        <v>7.665998085</v>
+        <v>7.605657702</v>
       </c>
       <c r="Q7">
-        <v>11.645998085</v>
+        <v>11.585657702</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08725442580582862</v>
+        <v>0.08761506555260085</v>
       </c>
       <c r="T7">
-        <v>0.7592523668267672</v>
+        <v>0.7658576104403482</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2021,7 +2021,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>26.40917940477772</v>
+        <v>22.00764950398144</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08480274161944479</v>
+        <v>0.08467662872335241</v>
       </c>
       <c r="C8">
-        <v>142.7333268119101</v>
+        <v>141.7313875794925</v>
       </c>
       <c r="D8">
-        <v>147.6793268119101</v>
+        <v>148.1583875794925</v>
       </c>
       <c r="E8">
-        <v>-105.814</v>
+        <v>-104.333</v>
       </c>
       <c r="F8">
-        <v>8.885999999999999</v>
+        <v>10.367</v>
       </c>
       <c r="G8">
         <v>3.94</v>
@@ -2065,28 +2065,28 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M8">
-        <v>0.4469657999999999</v>
+        <v>0.5214601</v>
       </c>
       <c r="N8">
-        <v>9.389700866666667</v>
+        <v>9.315206566666665</v>
       </c>
       <c r="O8">
-        <v>1.784043164666667</v>
+        <v>1.769889247666667</v>
       </c>
       <c r="P8">
-        <v>7.605657702</v>
+        <v>7.545317318999999</v>
       </c>
       <c r="Q8">
-        <v>11.585657702</v>
+        <v>11.525317319</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08761506555260085</v>
+        <v>0.08798346099285205</v>
       </c>
       <c r="T8">
-        <v>0.7658576104403482</v>
+        <v>0.7726049023036836</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>22.00764950398144</v>
+        <v>18.86369957484123</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2111,22 +2111,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08467662872335241</v>
+        <v>0.08455051582726002</v>
       </c>
       <c r="C9">
-        <v>141.7313875794925</v>
+        <v>140.73256653735</v>
       </c>
       <c r="D9">
-        <v>148.1583875794925</v>
+        <v>148.64056653735</v>
       </c>
       <c r="E9">
-        <v>-104.333</v>
+        <v>-102.852</v>
       </c>
       <c r="F9">
-        <v>10.367</v>
+        <v>11.848</v>
       </c>
       <c r="G9">
         <v>3.94</v>
@@ -2147,28 +2147,28 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M9">
-        <v>0.5214601</v>
+        <v>0.5959543999999999</v>
       </c>
       <c r="N9">
-        <v>9.315206566666665</v>
+        <v>9.240712266666666</v>
       </c>
       <c r="O9">
-        <v>1.769889247666667</v>
+        <v>1.755735330666667</v>
       </c>
       <c r="P9">
-        <v>7.545317318999999</v>
+        <v>7.484976935999999</v>
       </c>
       <c r="Q9">
-        <v>11.525317319</v>
+        <v>11.464976936</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08798346099285205</v>
+        <v>0.08835986502963045</v>
       </c>
       <c r="T9">
-        <v>0.7726049023036836</v>
+        <v>0.7794988744249176</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>18.86369957484123</v>
+        <v>16.50573712798608</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2193,22 +2193,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08455051582726002</v>
+        <v>0.08442440293116761</v>
       </c>
       <c r="C10">
-        <v>140.73256653735</v>
+        <v>139.7368942291786</v>
       </c>
       <c r="D10">
-        <v>148.64056653735</v>
+        <v>149.1258942291786</v>
       </c>
       <c r="E10">
-        <v>-102.852</v>
+        <v>-101.371</v>
       </c>
       <c r="F10">
-        <v>11.848</v>
+        <v>13.329</v>
       </c>
       <c r="G10">
         <v>3.94</v>
@@ -2229,28 +2229,28 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M10">
-        <v>0.5959543999999999</v>
+        <v>0.6704486999999999</v>
       </c>
       <c r="N10">
-        <v>9.240712266666666</v>
+        <v>9.166217966666666</v>
       </c>
       <c r="O10">
-        <v>1.755735330666667</v>
+        <v>1.741581413666667</v>
       </c>
       <c r="P10">
-        <v>7.484976935999999</v>
+        <v>7.424636553</v>
       </c>
       <c r="Q10">
-        <v>11.464976936</v>
+        <v>11.404636553</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08835986502963045</v>
+        <v>0.08874454168260176</v>
       </c>
       <c r="T10">
-        <v>0.7794988744249176</v>
+        <v>0.7865443624169478</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>16.50573712798608</v>
+        <v>14.67176633598763</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2275,22 +2275,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08442440293116761</v>
+        <v>0.08429829003507522</v>
       </c>
       <c r="C11">
-        <v>139.7368942291786</v>
+        <v>138.7444015988949</v>
       </c>
       <c r="D11">
-        <v>149.1258942291786</v>
+        <v>149.6144015988949</v>
       </c>
       <c r="E11">
-        <v>-101.371</v>
+        <v>-99.89</v>
       </c>
       <c r="F11">
-        <v>13.329</v>
+        <v>14.81</v>
       </c>
       <c r="G11">
         <v>3.94</v>
@@ -2311,28 +2311,28 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M11">
-        <v>0.6704486999999999</v>
+        <v>0.7449429999999999</v>
       </c>
       <c r="N11">
-        <v>9.166217966666666</v>
+        <v>9.091723666666667</v>
       </c>
       <c r="O11">
-        <v>1.741581413666667</v>
+        <v>1.727427496666667</v>
       </c>
       <c r="P11">
-        <v>7.424636553</v>
+        <v>7.36429617</v>
       </c>
       <c r="Q11">
-        <v>11.404636553</v>
+        <v>11.34429617</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08874454168260176</v>
+        <v>0.08913776670563912</v>
       </c>
       <c r="T11">
-        <v>0.7865443624169478</v>
+        <v>0.7937464168088012</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2349,7 +2349,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>14.67176633598763</v>
+        <v>13.20458970238886</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2357,22 +2357,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08429829003507522</v>
+        <v>0.08430582713898281</v>
       </c>
       <c r="C12">
-        <v>138.7444015988949</v>
+        <v>137.2341161796555</v>
       </c>
       <c r="D12">
-        <v>149.6144015988949</v>
+        <v>149.5851161796555</v>
       </c>
       <c r="E12">
-        <v>-99.89</v>
+        <v>-98.40900000000001</v>
       </c>
       <c r="F12">
-        <v>14.81</v>
+        <v>16.291</v>
       </c>
       <c r="G12">
         <v>3.94</v>
@@ -2393,45 +2393,45 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M12">
-        <v>0.744943</v>
+        <v>0.8438738</v>
       </c>
       <c r="N12">
-        <v>9.091723666666667</v>
+        <v>8.992792866666665</v>
       </c>
       <c r="O12">
-        <v>1.727427496666667</v>
+        <v>1.708630644666666</v>
       </c>
       <c r="P12">
-        <v>7.36429617</v>
+        <v>7.284162221999999</v>
       </c>
       <c r="Q12">
-        <v>11.34429617</v>
+        <v>11.264162222</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08913776670563912</v>
+        <v>0.0895398282460481</v>
       </c>
       <c r="T12">
-        <v>0.7937464168088012</v>
+        <v>0.8011103151195723</v>
       </c>
       <c r="U12">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V12">
         <v>0.19</v>
       </c>
       <c r="W12">
-        <v>0.040743</v>
+        <v>0.041958</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y12">
-        <v>13.20458970238886</v>
+        <v>11.65656128519059</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2439,22 +2439,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08430582713898281</v>
+        <v>0.08419186424289041</v>
       </c>
       <c r="C13">
-        <v>137.2341161796555</v>
+        <v>136.1971465331778</v>
       </c>
       <c r="D13">
-        <v>149.5851161796555</v>
+        <v>150.0291465331778</v>
       </c>
       <c r="E13">
-        <v>-98.40900000000001</v>
+        <v>-96.928</v>
       </c>
       <c r="F13">
-        <v>16.291</v>
+        <v>17.772</v>
       </c>
       <c r="G13">
         <v>3.94</v>
@@ -2475,28 +2475,28 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M13">
-        <v>0.8438738</v>
+        <v>0.9205895999999999</v>
       </c>
       <c r="N13">
-        <v>8.992792866666665</v>
+        <v>8.916077066666666</v>
       </c>
       <c r="O13">
-        <v>1.708630644666666</v>
+        <v>1.694054642666667</v>
       </c>
       <c r="P13">
-        <v>7.284162221999999</v>
+        <v>7.222022423999999</v>
       </c>
       <c r="Q13">
-        <v>11.264162222</v>
+        <v>11.202022424</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.0895398282460481</v>
+        <v>0.0899510275487391</v>
       </c>
       <c r="T13">
-        <v>0.8011103151195723</v>
+        <v>0.8086415747555884</v>
       </c>
       <c r="U13">
         <v>0.0518</v>
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>11.65656128519059</v>
+        <v>10.68518117809137</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2521,22 +2521,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08419186424289041</v>
+        <v>0.08407790134679802</v>
       </c>
       <c r="C14">
-        <v>136.1971465331778</v>
+        <v>135.1628208657721</v>
       </c>
       <c r="D14">
-        <v>150.0291465331778</v>
+        <v>150.4758208657721</v>
       </c>
       <c r="E14">
-        <v>-96.928</v>
+        <v>-95.447</v>
       </c>
       <c r="F14">
-        <v>17.772</v>
+        <v>19.253</v>
       </c>
       <c r="G14">
         <v>3.94</v>
@@ -2557,28 +2557,28 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M14">
-        <v>0.9205895999999999</v>
+        <v>0.9973054</v>
       </c>
       <c r="N14">
-        <v>8.916077066666666</v>
+        <v>8.839361266666666</v>
       </c>
       <c r="O14">
-        <v>1.694054642666667</v>
+        <v>1.679478640666667</v>
       </c>
       <c r="P14">
-        <v>7.222022423999999</v>
+        <v>7.159882625999999</v>
       </c>
       <c r="Q14">
-        <v>11.202022424</v>
+        <v>11.139882626</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.0899510275487391</v>
+        <v>0.09037167970896323</v>
       </c>
       <c r="T14">
-        <v>0.8086415747555884</v>
+        <v>0.8163459667970302</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2595,7 +2595,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>10.68518117809137</v>
+        <v>9.863244164392036</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2603,22 +2603,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08407790134679802</v>
+        <v>0.08415671845070562</v>
       </c>
       <c r="C15">
-        <v>135.1628208657721</v>
+        <v>133.3726164059589</v>
       </c>
       <c r="D15">
-        <v>150.4758208657721</v>
+        <v>150.1666164059589</v>
       </c>
       <c r="E15">
-        <v>-95.447</v>
+        <v>-93.96600000000001</v>
       </c>
       <c r="F15">
-        <v>19.253</v>
+        <v>20.734</v>
       </c>
       <c r="G15">
         <v>3.94</v>
@@ -2639,45 +2639,45 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M15">
-        <v>0.9973054</v>
+        <v>1.109269</v>
       </c>
       <c r="N15">
-        <v>8.839361266666666</v>
+        <v>8.727397666666667</v>
       </c>
       <c r="O15">
-        <v>1.679478640666667</v>
+        <v>1.658205556666667</v>
       </c>
       <c r="P15">
-        <v>7.159882625999999</v>
+        <v>7.069192109999999</v>
       </c>
       <c r="Q15">
-        <v>11.139882626</v>
+        <v>11.04919211</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09037167970896323</v>
+        <v>0.09080211447756467</v>
       </c>
       <c r="T15">
-        <v>0.8163459667970302</v>
+        <v>0.8242295307464125</v>
       </c>
       <c r="U15">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V15">
         <v>0.19</v>
       </c>
       <c r="W15">
-        <v>0.041958</v>
+        <v>0.04333500000000001</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y15">
-        <v>9.863244164392036</v>
+        <v>8.867701762752468</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2685,22 +2685,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08415671845070562</v>
+        <v>0.08405652555461322</v>
       </c>
       <c r="C16">
-        <v>133.3726164059589</v>
+        <v>132.2848990675699</v>
       </c>
       <c r="D16">
-        <v>150.1666164059589</v>
+        <v>150.5598990675699</v>
       </c>
       <c r="E16">
-        <v>-93.96600000000001</v>
+        <v>-92.485</v>
       </c>
       <c r="F16">
-        <v>20.734</v>
+        <v>22.215</v>
       </c>
       <c r="G16">
         <v>3.94</v>
@@ -2721,28 +2721,28 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M16">
-        <v>1.109269</v>
+        <v>1.1885025</v>
       </c>
       <c r="N16">
-        <v>8.727397666666667</v>
+        <v>8.648164166666666</v>
       </c>
       <c r="O16">
-        <v>1.658205556666667</v>
+        <v>1.643151191666667</v>
       </c>
       <c r="P16">
-        <v>7.069192109999999</v>
+        <v>7.005012975</v>
       </c>
       <c r="Q16">
-        <v>11.04919211</v>
+        <v>10.985012975</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09080211447756467</v>
+        <v>0.09124267712307438</v>
       </c>
       <c r="T16">
-        <v>0.8242295307464125</v>
+        <v>0.8322985903181331</v>
       </c>
       <c r="U16">
         <v>0.0535</v>
@@ -2759,7 +2759,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>8.867701762752468</v>
+        <v>8.276521645235633</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2767,22 +2767,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08405652555461322</v>
+        <v>0.0839563326585208</v>
       </c>
       <c r="C17">
-        <v>132.2848990675699</v>
+        <v>131.1992471335899</v>
       </c>
       <c r="D17">
-        <v>150.5598990675699</v>
+        <v>150.9552471335899</v>
       </c>
       <c r="E17">
-        <v>-92.485</v>
+        <v>-91.004</v>
       </c>
       <c r="F17">
-        <v>22.215</v>
+        <v>23.696</v>
       </c>
       <c r="G17">
         <v>3.94</v>
@@ -2803,28 +2803,28 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M17">
-        <v>1.1885025</v>
+        <v>1.267736</v>
       </c>
       <c r="N17">
-        <v>8.648164166666666</v>
+        <v>8.568930666666667</v>
       </c>
       <c r="O17">
-        <v>1.643151191666667</v>
+        <v>1.628096826666667</v>
       </c>
       <c r="P17">
-        <v>7.005012975</v>
+        <v>6.94083384</v>
       </c>
       <c r="Q17">
-        <v>10.985012975</v>
+        <v>10.92083384</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09124267712307438</v>
+        <v>0.09169372935538192</v>
       </c>
       <c r="T17">
-        <v>0.8322985903181331</v>
+        <v>0.8405597703558471</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.276521645235636</v>
+        <v>7.759239042408409</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2849,22 +2849,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.0839563326585208</v>
+        <v>0.08396629976242842</v>
       </c>
       <c r="C18">
-        <v>131.1992471335899</v>
+        <v>129.6788252707699</v>
       </c>
       <c r="D18">
-        <v>150.9552471335899</v>
+        <v>150.9158252707699</v>
       </c>
       <c r="E18">
-        <v>-91.004</v>
+        <v>-89.523</v>
       </c>
       <c r="F18">
-        <v>23.696</v>
+        <v>25.177</v>
       </c>
       <c r="G18">
         <v>3.94</v>
@@ -2885,45 +2885,45 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M18">
-        <v>1.267736</v>
+        <v>1.3671111</v>
       </c>
       <c r="N18">
-        <v>8.568930666666667</v>
+        <v>8.469555566666665</v>
       </c>
       <c r="O18">
-        <v>1.628096826666667</v>
+        <v>1.609215557666666</v>
       </c>
       <c r="P18">
-        <v>6.94083384</v>
+        <v>6.860340008999999</v>
       </c>
       <c r="Q18">
-        <v>10.92083384</v>
+        <v>10.840340009</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09169372935538192</v>
+        <v>0.09215565031617882</v>
       </c>
       <c r="T18">
-        <v>0.8405597703558471</v>
+        <v>0.8490200149727831</v>
       </c>
       <c r="U18">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V18">
         <v>0.19</v>
       </c>
       <c r="W18">
-        <v>0.04333500000000001</v>
+        <v>0.043983</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y18">
-        <v>7.759239042408409</v>
+        <v>7.19522112479861</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2931,22 +2931,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08396629976242842</v>
+        <v>0.083872586866336</v>
       </c>
       <c r="C19">
-        <v>129.6788252707699</v>
+        <v>128.569293568996</v>
       </c>
       <c r="D19">
-        <v>150.9158252707699</v>
+        <v>151.287293568996</v>
       </c>
       <c r="E19">
-        <v>-89.523</v>
+        <v>-88.042</v>
       </c>
       <c r="F19">
-        <v>25.177</v>
+        <v>26.658</v>
       </c>
       <c r="G19">
         <v>3.94</v>
@@ -2967,28 +2967,28 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M19">
-        <v>1.3671111</v>
+        <v>1.4475294</v>
       </c>
       <c r="N19">
-        <v>8.469555566666665</v>
+        <v>8.389137266666665</v>
       </c>
       <c r="O19">
-        <v>1.609215557666666</v>
+        <v>1.593936080666666</v>
       </c>
       <c r="P19">
-        <v>6.860340008999999</v>
+        <v>6.795201185999999</v>
       </c>
       <c r="Q19">
-        <v>10.840340009</v>
+        <v>10.775201186</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09215565031617882</v>
+        <v>0.09262883764187319</v>
       </c>
       <c r="T19">
-        <v>0.8490200149727831</v>
+        <v>0.8576866070194004</v>
       </c>
       <c r="U19">
         <v>0.0543</v>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>7.19522112479861</v>
+        <v>6.795486617865354</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3013,22 +3013,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08387258686633602</v>
+        <v>0.08377887397024363</v>
       </c>
       <c r="C20">
-        <v>128.569293568996</v>
+        <v>127.4615950637543</v>
       </c>
       <c r="D20">
-        <v>151.2872935689959</v>
+        <v>151.6605950637543</v>
       </c>
       <c r="E20">
-        <v>-88.042</v>
+        <v>-86.56100000000001</v>
       </c>
       <c r="F20">
-        <v>26.658</v>
+        <v>28.139</v>
       </c>
       <c r="G20">
         <v>3.94</v>
@@ -3049,28 +3049,28 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M20">
-        <v>1.4475294</v>
+        <v>1.5279477</v>
       </c>
       <c r="N20">
-        <v>8.389137266666665</v>
+        <v>8.308718966666666</v>
       </c>
       <c r="O20">
-        <v>1.593936080666666</v>
+        <v>1.578656603666666</v>
       </c>
       <c r="P20">
-        <v>6.795201185999999</v>
+        <v>6.730062362999999</v>
       </c>
       <c r="Q20">
-        <v>10.775201186</v>
+        <v>10.710062363</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09262883764187319</v>
+        <v>0.09311370860523904</v>
       </c>
       <c r="T20">
-        <v>0.8576866070194004</v>
+        <v>0.8665671889930947</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -3087,7 +3087,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>6.795486617865355</v>
+        <v>6.437829427451389</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08377887397024363</v>
+        <v>0.08368516107415123</v>
       </c>
       <c r="C21">
-        <v>127.4615950637543</v>
+        <v>126.3557433588533</v>
       </c>
       <c r="D21">
-        <v>151.6605950637543</v>
+        <v>152.0357433588533</v>
       </c>
       <c r="E21">
-        <v>-86.56100000000001</v>
+        <v>-85.08</v>
       </c>
       <c r="F21">
-        <v>28.139</v>
+        <v>29.62</v>
       </c>
       <c r="G21">
         <v>3.94</v>
@@ -3131,28 +3131,28 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M21">
-        <v>1.5279477</v>
+        <v>1.608366</v>
       </c>
       <c r="N21">
-        <v>8.308718966666666</v>
+        <v>8.228300666666666</v>
       </c>
       <c r="O21">
-        <v>1.578656603666666</v>
+        <v>1.563377126666667</v>
       </c>
       <c r="P21">
-        <v>6.730062362999999</v>
+        <v>6.664923539999999</v>
       </c>
       <c r="Q21">
-        <v>10.710062363</v>
+        <v>10.64492354</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09311370860523904</v>
+        <v>0.09361070134268903</v>
       </c>
       <c r="T21">
-        <v>0.8665671889930947</v>
+        <v>0.8756697855161316</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3169,7 +3169,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>6.437829427451389</v>
+        <v>6.115937956078819</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3177,22 +3177,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08368516107415123</v>
+        <v>0.08376154817805884</v>
       </c>
       <c r="C22">
-        <v>126.3557433588533</v>
+        <v>124.5688135250344</v>
       </c>
       <c r="D22">
-        <v>152.0357433588533</v>
+        <v>151.7298135250344</v>
       </c>
       <c r="E22">
-        <v>-85.08</v>
+        <v>-83.599</v>
       </c>
       <c r="F22">
-        <v>29.62</v>
+        <v>31.101</v>
       </c>
       <c r="G22">
         <v>3.94</v>
@@ -3213,45 +3213,45 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M22">
-        <v>1.608366</v>
+        <v>1.7198853</v>
       </c>
       <c r="N22">
-        <v>8.228300666666666</v>
+        <v>8.116781366666666</v>
       </c>
       <c r="O22">
-        <v>1.563377126666667</v>
+        <v>1.542188459666667</v>
       </c>
       <c r="P22">
-        <v>6.664923539999999</v>
+        <v>6.574592907</v>
       </c>
       <c r="Q22">
-        <v>10.64492354</v>
+        <v>10.554592907</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09361070134268903</v>
+        <v>0.09412027617475802</v>
       </c>
       <c r="T22">
-        <v>0.8756697855161316</v>
+        <v>0.8850028275207641</v>
       </c>
       <c r="U22">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V22">
         <v>0.19</v>
       </c>
       <c r="W22">
-        <v>0.043983</v>
+        <v>0.04479300000000001</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y22">
-        <v>6.115937956078819</v>
+        <v>5.719373650479287</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3259,22 +3259,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08376154817805884</v>
+        <v>0.08367593528196642</v>
       </c>
       <c r="C23">
-        <v>124.5688135250344</v>
+        <v>123.4307761123009</v>
       </c>
       <c r="D23">
-        <v>151.7298135250344</v>
+        <v>152.0727761123009</v>
       </c>
       <c r="E23">
-        <v>-83.599</v>
+        <v>-82.11799999999999</v>
       </c>
       <c r="F23">
-        <v>31.101</v>
+        <v>32.582</v>
       </c>
       <c r="G23">
         <v>3.94</v>
@@ -3295,28 +3295,28 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M23">
-        <v>1.7198853</v>
+        <v>1.8017846</v>
       </c>
       <c r="N23">
-        <v>8.116781366666666</v>
+        <v>8.034882066666666</v>
       </c>
       <c r="O23">
-        <v>1.542188459666667</v>
+        <v>1.526627592666667</v>
       </c>
       <c r="P23">
-        <v>6.574592907</v>
+        <v>6.508254474</v>
       </c>
       <c r="Q23">
-        <v>10.554592907</v>
+        <v>10.488254474</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09412027617475802</v>
+        <v>0.09464291702816208</v>
       </c>
       <c r="T23">
-        <v>0.8850028275207641</v>
+        <v>0.8945751782947462</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3333,7 +3333,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.719373650479288</v>
+        <v>5.459402120912048</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3341,22 +3341,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08367593528196642</v>
+        <v>0.08359032238587402</v>
       </c>
       <c r="C24">
-        <v>123.4307761123009</v>
+        <v>122.2942926434605</v>
       </c>
       <c r="D24">
-        <v>152.0727761123009</v>
+        <v>152.4172926434605</v>
       </c>
       <c r="E24">
-        <v>-82.11799999999999</v>
+        <v>-80.637</v>
       </c>
       <c r="F24">
-        <v>32.582</v>
+        <v>34.063</v>
       </c>
       <c r="G24">
         <v>3.94</v>
@@ -3377,28 +3377,28 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M24">
-        <v>1.8017846</v>
+        <v>1.8836839</v>
       </c>
       <c r="N24">
-        <v>8.034882066666666</v>
+        <v>7.952982766666666</v>
       </c>
       <c r="O24">
-        <v>1.526627592666667</v>
+        <v>1.511066725666667</v>
       </c>
       <c r="P24">
-        <v>6.508254474</v>
+        <v>6.441916040999999</v>
       </c>
       <c r="Q24">
-        <v>10.488254474</v>
+        <v>10.421916041</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09464291702816208</v>
+        <v>0.09517913296866756</v>
       </c>
       <c r="T24">
-        <v>0.8945751782947462</v>
+        <v>0.9043961615563643</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3415,7 +3415,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.459402120912048</v>
+        <v>5.222036811307175</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3423,22 +3423,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08359032238587402</v>
+        <v>0.08350470948978164</v>
       </c>
       <c r="C25">
-        <v>122.2942926434605</v>
+        <v>121.1593737037403</v>
       </c>
       <c r="D25">
-        <v>152.4172926434605</v>
+        <v>152.7633737037403</v>
       </c>
       <c r="E25">
-        <v>-80.637</v>
+        <v>-79.15600000000001</v>
       </c>
       <c r="F25">
-        <v>34.063</v>
+        <v>35.544</v>
       </c>
       <c r="G25">
         <v>3.94</v>
@@ -3459,28 +3459,28 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M25">
-        <v>1.8836839</v>
+        <v>1.9655832</v>
       </c>
       <c r="N25">
-        <v>7.952982766666666</v>
+        <v>7.871083466666666</v>
       </c>
       <c r="O25">
-        <v>1.511066725666667</v>
+        <v>1.495505858666667</v>
       </c>
       <c r="P25">
-        <v>6.441916040999999</v>
+        <v>6.375577608</v>
       </c>
       <c r="Q25">
-        <v>10.421916041</v>
+        <v>10.355577608</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09517913296866756</v>
+        <v>0.09572945985497583</v>
       </c>
       <c r="T25">
-        <v>0.9043961615563643</v>
+        <v>0.9144755917459196</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.222036811307175</v>
+        <v>5.004451944169377</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3505,22 +3505,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08350470948978164</v>
+        <v>0.08341909659368925</v>
       </c>
       <c r="C26">
-        <v>121.1593737037403</v>
+        <v>120.0260299747262</v>
       </c>
       <c r="D26">
-        <v>152.7633737037403</v>
+        <v>153.1110299747263</v>
       </c>
       <c r="E26">
-        <v>-79.15600000000001</v>
+        <v>-77.67500000000001</v>
       </c>
       <c r="F26">
-        <v>35.544</v>
+        <v>37.025</v>
       </c>
       <c r="G26">
         <v>3.94</v>
@@ -3541,28 +3541,28 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M26">
-        <v>1.9655832</v>
+        <v>2.0474825</v>
       </c>
       <c r="N26">
-        <v>7.871083466666666</v>
+        <v>7.789184166666666</v>
       </c>
       <c r="O26">
-        <v>1.495505858666667</v>
+        <v>1.479944991666666</v>
       </c>
       <c r="P26">
-        <v>6.375577608</v>
+        <v>6.309239174999999</v>
       </c>
       <c r="Q26">
-        <v>10.355577608</v>
+        <v>10.289239175</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09572945985497583</v>
+        <v>0.09629446212491899</v>
       </c>
       <c r="T26">
-        <v>0.9144755917459196</v>
+        <v>0.9248238067405298</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.004451944169377</v>
+        <v>4.804273866402601</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3587,22 +3587,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08341909659368925</v>
+        <v>0.08333348369759684</v>
       </c>
       <c r="C27">
-        <v>120.0260299747262</v>
+        <v>118.8942722354617</v>
       </c>
       <c r="D27">
-        <v>153.1110299747263</v>
+        <v>153.4602722354617</v>
       </c>
       <c r="E27">
-        <v>-77.67500000000001</v>
+        <v>-76.194</v>
       </c>
       <c r="F27">
-        <v>37.025</v>
+        <v>38.506</v>
       </c>
       <c r="G27">
         <v>3.94</v>
@@ -3623,28 +3623,28 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M27">
-        <v>2.0474825</v>
+        <v>2.1293818</v>
       </c>
       <c r="N27">
-        <v>7.789184166666666</v>
+        <v>7.707284866666666</v>
       </c>
       <c r="O27">
-        <v>1.479944991666666</v>
+        <v>1.464384124666666</v>
       </c>
       <c r="P27">
-        <v>6.309239174999999</v>
+        <v>6.242900742</v>
       </c>
       <c r="Q27">
-        <v>10.289239175</v>
+        <v>10.222900742</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09629446212491899</v>
+        <v>0.09687473472648221</v>
       </c>
       <c r="T27">
-        <v>0.9248238067405298</v>
+        <v>0.9354517032214807</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3661,7 +3661,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.804273866402601</v>
+        <v>4.619494102310195</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3669,22 +3669,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08333348369759684</v>
+        <v>0.08379462080150443</v>
       </c>
       <c r="C28">
-        <v>118.8942722354617</v>
+        <v>115.5507394871225</v>
       </c>
       <c r="D28">
-        <v>153.4602722354617</v>
+        <v>151.5977394871225</v>
       </c>
       <c r="E28">
-        <v>-76.194</v>
+        <v>-74.71299999999999</v>
       </c>
       <c r="F28">
-        <v>38.506</v>
+        <v>39.987</v>
       </c>
       <c r="G28">
         <v>3.94</v>
@@ -3705,45 +3705,45 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M28">
-        <v>2.1293818</v>
+        <v>2.3112486</v>
       </c>
       <c r="N28">
-        <v>7.707284866666666</v>
+        <v>7.525418066666665</v>
       </c>
       <c r="O28">
-        <v>1.464384124666666</v>
+        <v>1.429829432666667</v>
       </c>
       <c r="P28">
-        <v>6.242900742</v>
+        <v>6.095588633999999</v>
       </c>
       <c r="Q28">
-        <v>10.222900742</v>
+        <v>10.075588634</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09687473472648221</v>
+        <v>0.09747090520754031</v>
       </c>
       <c r="T28">
-        <v>0.9354517032214807</v>
+        <v>0.9463707749484851</v>
       </c>
       <c r="U28">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V28">
         <v>0.19</v>
       </c>
       <c r="W28">
-        <v>0.04479300000000001</v>
+        <v>0.04681800000000001</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y28">
-        <v>4.619494102310195</v>
+        <v>4.255996809112903</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3751,22 +3751,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08379462080150443</v>
+        <v>0.08372925790541202</v>
       </c>
       <c r="C29">
-        <v>115.5507394871225</v>
+        <v>114.3309854972251</v>
       </c>
       <c r="D29">
-        <v>151.5977394871225</v>
+        <v>151.8589854972251</v>
       </c>
       <c r="E29">
-        <v>-74.71299999999999</v>
+        <v>-73.232</v>
       </c>
       <c r="F29">
-        <v>39.987</v>
+        <v>41.468</v>
       </c>
       <c r="G29">
         <v>3.94</v>
@@ -3787,28 +3787,28 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M29">
-        <v>2.3112486</v>
+        <v>2.3968504</v>
       </c>
       <c r="N29">
-        <v>7.525418066666665</v>
+        <v>7.439816266666666</v>
       </c>
       <c r="O29">
-        <v>1.429829432666667</v>
+        <v>1.413565090666667</v>
       </c>
       <c r="P29">
-        <v>6.095588633999999</v>
+        <v>6.026251176</v>
       </c>
       <c r="Q29">
-        <v>10.075588634</v>
+        <v>10.006251176</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09747090520754031</v>
+        <v>0.09808363597973893</v>
       </c>
       <c r="T29">
-        <v>0.9463707749484851</v>
+        <v>0.9575931542234618</v>
       </c>
       <c r="U29">
         <v>0.0578</v>
@@ -3825,7 +3825,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.255996809112903</v>
+        <v>4.103996923073156</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3833,22 +3833,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08372925790541202</v>
+        <v>0.08448604500931965</v>
       </c>
       <c r="C30">
-        <v>114.3309854972251</v>
+        <v>109.8792780545514</v>
       </c>
       <c r="D30">
-        <v>151.8589854972251</v>
+        <v>148.8882780545514</v>
       </c>
       <c r="E30">
-        <v>-73.232</v>
+        <v>-71.751</v>
       </c>
       <c r="F30">
-        <v>41.468</v>
+        <v>42.94900000000001</v>
       </c>
       <c r="G30">
         <v>3.94</v>
@@ -3869,45 +3869,45 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M30">
-        <v>2.3968504</v>
+        <v>2.6327737</v>
       </c>
       <c r="N30">
-        <v>7.439816266666666</v>
+        <v>7.203892966666666</v>
       </c>
       <c r="O30">
-        <v>1.413565090666667</v>
+        <v>1.368739663666666</v>
       </c>
       <c r="P30">
-        <v>6.026251176</v>
+        <v>5.835153302999999</v>
       </c>
       <c r="Q30">
-        <v>10.006251176</v>
+        <v>9.815153302999999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09808363597973893</v>
+        <v>0.09871362677368964</v>
       </c>
       <c r="T30">
-        <v>0.9575931542234618</v>
+        <v>0.9691316568582973</v>
       </c>
       <c r="U30">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V30">
         <v>0.19</v>
       </c>
       <c r="W30">
-        <v>0.04681800000000001</v>
+        <v>0.049653</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y30">
-        <v>4.103996923073156</v>
+        <v>3.736237059290992</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3915,22 +3915,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08448604500931964</v>
+        <v>0.08444903211322724</v>
       </c>
       <c r="C31">
-        <v>109.8792780545515</v>
+        <v>108.5408634199201</v>
       </c>
       <c r="D31">
-        <v>148.8882780545515</v>
+        <v>149.0308634199201</v>
       </c>
       <c r="E31">
-        <v>-71.751</v>
+        <v>-70.27000000000001</v>
       </c>
       <c r="F31">
-        <v>42.949</v>
+        <v>44.43</v>
       </c>
       <c r="G31">
         <v>3.94</v>
@@ -3951,28 +3951,28 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M31">
-        <v>2.6327737</v>
+        <v>2.723559</v>
       </c>
       <c r="N31">
-        <v>7.203892966666666</v>
+        <v>7.113107666666666</v>
       </c>
       <c r="O31">
-        <v>1.368739663666667</v>
+        <v>1.351490456666667</v>
       </c>
       <c r="P31">
-        <v>5.835153303</v>
+        <v>5.76161721</v>
       </c>
       <c r="Q31">
-        <v>9.815153302999999</v>
+        <v>9.741617209999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09871362677368964</v>
+        <v>0.09936161730461035</v>
       </c>
       <c r="T31">
-        <v>0.9691316568582972</v>
+        <v>0.980999830996985</v>
       </c>
       <c r="U31">
         <v>0.0613</v>
@@ -3989,7 +3989,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.736237059290993</v>
+        <v>3.611695823981293</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3997,22 +3997,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08444903211322724</v>
+        <v>0.08511509921713485</v>
       </c>
       <c r="C32">
-        <v>108.5408634199201</v>
+        <v>104.5350178118059</v>
       </c>
       <c r="D32">
-        <v>149.0308634199201</v>
+        <v>146.5060178118059</v>
       </c>
       <c r="E32">
-        <v>-70.27000000000001</v>
+        <v>-68.789</v>
       </c>
       <c r="F32">
-        <v>44.43</v>
+        <v>45.911</v>
       </c>
       <c r="G32">
         <v>3.94</v>
@@ -4033,45 +4033,45 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M32">
-        <v>2.723559</v>
+        <v>2.9428951</v>
       </c>
       <c r="N32">
-        <v>7.113107666666666</v>
+        <v>6.893771566666666</v>
       </c>
       <c r="O32">
-        <v>1.351490456666667</v>
+        <v>1.309816597666666</v>
       </c>
       <c r="P32">
-        <v>5.76161721</v>
+        <v>5.583954968999999</v>
       </c>
       <c r="Q32">
-        <v>9.741617209999999</v>
+        <v>9.563954968999997</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09936161730461035</v>
+        <v>0.1000283901697606</v>
       </c>
       <c r="T32">
-        <v>0.980999830996985</v>
+        <v>0.9932120101831708</v>
       </c>
       <c r="U32">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V32">
         <v>0.19</v>
       </c>
       <c r="W32">
-        <v>0.049653</v>
+        <v>0.05192100000000001</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y32">
-        <v>3.611695823981293</v>
+        <v>3.342513522370086</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4079,22 +4079,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08511509921713485</v>
+        <v>0.08510076632104244</v>
       </c>
       <c r="C33">
-        <v>104.5350178118059</v>
+        <v>103.1074482083803</v>
       </c>
       <c r="D33">
-        <v>146.5060178118059</v>
+        <v>146.5594482083803</v>
       </c>
       <c r="E33">
-        <v>-68.789</v>
+        <v>-67.30800000000001</v>
       </c>
       <c r="F33">
-        <v>45.911</v>
+        <v>47.392</v>
       </c>
       <c r="G33">
         <v>3.94</v>
@@ -4115,28 +4115,28 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M33">
-        <v>2.9428951</v>
+        <v>3.0378272</v>
       </c>
       <c r="N33">
-        <v>6.893771566666666</v>
+        <v>6.798839466666666</v>
       </c>
       <c r="O33">
-        <v>1.309816597666666</v>
+        <v>1.291779498666667</v>
       </c>
       <c r="P33">
-        <v>5.583954968999999</v>
+        <v>5.507059968</v>
       </c>
       <c r="Q33">
-        <v>9.563954968999997</v>
+        <v>9.487059968000001</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1000283901697606</v>
+        <v>0.100714774001533</v>
       </c>
       <c r="T33">
-        <v>0.9932120101831708</v>
+        <v>1.005783371110127</v>
       </c>
       <c r="U33">
         <v>0.0641</v>
@@ -4153,7 +4153,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.342513522370086</v>
+        <v>3.238059974796021</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08510076632104244</v>
+        <v>0.08508643342495005</v>
       </c>
       <c r="C34">
-        <v>103.1074482083803</v>
+        <v>101.6799175910501</v>
       </c>
       <c r="D34">
-        <v>146.5594482083803</v>
+        <v>146.6129175910501</v>
       </c>
       <c r="E34">
-        <v>-67.30800000000001</v>
+        <v>-65.827</v>
       </c>
       <c r="F34">
-        <v>47.392</v>
+        <v>48.873</v>
       </c>
       <c r="G34">
         <v>3.94</v>
@@ -4197,28 +4197,28 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M34">
-        <v>3.0378272</v>
+        <v>3.1327593</v>
       </c>
       <c r="N34">
-        <v>6.798839466666666</v>
+        <v>6.703907366666666</v>
       </c>
       <c r="O34">
-        <v>1.291779498666667</v>
+        <v>1.273742399666667</v>
       </c>
       <c r="P34">
-        <v>5.507059968</v>
+        <v>5.430164967</v>
       </c>
       <c r="Q34">
-        <v>9.487059968000001</v>
+        <v>9.410164967</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.100714774001533</v>
+        <v>0.1014216469029105</v>
       </c>
       <c r="T34">
-        <v>1.005783371110127</v>
+        <v>1.018729996542365</v>
       </c>
       <c r="U34">
         <v>0.0641</v>
@@ -4235,7 +4235,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.238059974796021</v>
+        <v>3.139936945256747</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4243,22 +4243,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08508643342495005</v>
+        <v>0.08507210052885764</v>
       </c>
       <c r="C35">
-        <v>101.6799175910501</v>
+        <v>100.2524260025009</v>
       </c>
       <c r="D35">
-        <v>146.6129175910501</v>
+        <v>146.6664260025009</v>
       </c>
       <c r="E35">
-        <v>-65.827</v>
+        <v>-64.346</v>
       </c>
       <c r="F35">
-        <v>48.873</v>
+        <v>50.354</v>
       </c>
       <c r="G35">
         <v>3.94</v>
@@ -4279,28 +4279,28 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M35">
-        <v>3.1327593</v>
+        <v>3.2276914</v>
       </c>
       <c r="N35">
-        <v>6.703907366666666</v>
+        <v>6.608975266666666</v>
       </c>
       <c r="O35">
-        <v>1.273742399666667</v>
+        <v>1.255705300666667</v>
       </c>
       <c r="P35">
-        <v>5.430164967</v>
+        <v>5.353269965999999</v>
       </c>
       <c r="Q35">
-        <v>9.410164967</v>
+        <v>9.333269966</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1014216469029105</v>
+        <v>0.1021499401952389</v>
       </c>
       <c r="T35">
-        <v>1.018729996542365</v>
+        <v>1.032068943957399</v>
       </c>
       <c r="U35">
         <v>0.0641</v>
@@ -4317,7 +4317,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.139936945256747</v>
+        <v>3.047585858631549</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4325,22 +4325,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08507210052885764</v>
+        <v>0.08726906763276523</v>
       </c>
       <c r="C36">
-        <v>100.2524260025009</v>
+        <v>91.0012654570875</v>
       </c>
       <c r="D36">
-        <v>146.6664260025009</v>
+        <v>138.8962654570875</v>
       </c>
       <c r="E36">
-        <v>-64.346</v>
+        <v>-62.865</v>
       </c>
       <c r="F36">
-        <v>50.354</v>
+        <v>51.835</v>
       </c>
       <c r="G36">
         <v>3.94</v>
@@ -4361,45 +4361,45 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M36">
-        <v>3.2276914</v>
+        <v>3.7269365</v>
       </c>
       <c r="N36">
-        <v>6.608975266666666</v>
+        <v>6.109730166666665</v>
       </c>
       <c r="O36">
-        <v>1.255705300666667</v>
+        <v>1.160848731666666</v>
       </c>
       <c r="P36">
-        <v>5.353269965999999</v>
+        <v>4.948881434999999</v>
       </c>
       <c r="Q36">
-        <v>9.333269966</v>
+        <v>8.928881434999997</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1021499401952389</v>
+        <v>0.1029006425119465</v>
       </c>
       <c r="T36">
-        <v>1.032068943957399</v>
+        <v>1.045818320523664</v>
       </c>
       <c r="U36">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V36">
         <v>0.19</v>
       </c>
       <c r="W36">
-        <v>0.05192100000000001</v>
+        <v>0.05823900000000001</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y36">
-        <v>3.047585858631549</v>
+        <v>2.639343779178064</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4407,22 +4407,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08726906763276523</v>
+        <v>0.08731791473667284</v>
       </c>
       <c r="C37">
-        <v>91.0012654570875</v>
+        <v>89.35684972789704</v>
       </c>
       <c r="D37">
-        <v>138.8962654570875</v>
+        <v>138.732849727897</v>
       </c>
       <c r="E37">
-        <v>-62.865</v>
+        <v>-61.384</v>
       </c>
       <c r="F37">
-        <v>51.835</v>
+        <v>53.316</v>
       </c>
       <c r="G37">
         <v>3.94</v>
@@ -4443,28 +4443,28 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M37">
-        <v>3.7269365</v>
+        <v>3.833420400000001</v>
       </c>
       <c r="N37">
-        <v>6.109730166666665</v>
+        <v>6.003246266666665</v>
       </c>
       <c r="O37">
-        <v>1.160848731666666</v>
+        <v>1.140616790666666</v>
       </c>
       <c r="P37">
-        <v>4.948881434999999</v>
+        <v>4.862629475999999</v>
       </c>
       <c r="Q37">
-        <v>8.928881434999997</v>
+        <v>8.842629475999999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1029006425119465</v>
+        <v>0.1036748042760513</v>
       </c>
       <c r="T37">
-        <v>1.045818320523664</v>
+        <v>1.059997365107625</v>
       </c>
       <c r="U37">
         <v>0.07190000000000001</v>
@@ -4481,7 +4481,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.639343779178064</v>
+        <v>2.566028674200895</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4489,22 +4489,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08731791473667286</v>
+        <v>0.08853559184058045</v>
       </c>
       <c r="C38">
-        <v>89.35684972789699</v>
+        <v>83.92289605631359</v>
       </c>
       <c r="D38">
-        <v>138.732849727897</v>
+        <v>134.7798960563136</v>
       </c>
       <c r="E38">
-        <v>-61.38400000000001</v>
+        <v>-59.90300000000001</v>
       </c>
       <c r="F38">
-        <v>53.316</v>
+        <v>54.797</v>
       </c>
       <c r="G38">
         <v>3.94</v>
@@ -4525,45 +4525,45 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M38">
-        <v>3.8334204</v>
+        <v>4.1536126</v>
       </c>
       <c r="N38">
-        <v>6.003246266666666</v>
+        <v>5.683054066666666</v>
       </c>
       <c r="O38">
-        <v>1.140616790666667</v>
+        <v>1.079780272666667</v>
       </c>
       <c r="P38">
-        <v>4.862629476</v>
+        <v>4.603273794</v>
       </c>
       <c r="Q38">
-        <v>8.842629475999999</v>
+        <v>8.583273794</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1036748042760513</v>
+        <v>0.1044735426040959</v>
       </c>
       <c r="T38">
-        <v>1.059997365107625</v>
+        <v>1.074626538091077</v>
       </c>
       <c r="U38">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V38">
         <v>0.19</v>
       </c>
       <c r="W38">
-        <v>0.05823900000000001</v>
+        <v>0.06139800000000001</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y38">
-        <v>2.566028674200895</v>
+        <v>2.368219575091492</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4571,22 +4571,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08853559184058045</v>
+        <v>0.08861602894448806</v>
       </c>
       <c r="C39">
-        <v>83.92289605631359</v>
+        <v>82.18868937715627</v>
       </c>
       <c r="D39">
-        <v>134.7798960563136</v>
+        <v>134.5266893771563</v>
       </c>
       <c r="E39">
-        <v>-59.90300000000001</v>
+        <v>-58.422</v>
       </c>
       <c r="F39">
-        <v>54.797</v>
+        <v>56.278</v>
       </c>
       <c r="G39">
         <v>3.94</v>
@@ -4607,28 +4607,28 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M39">
-        <v>4.1536126</v>
+        <v>4.2658724</v>
       </c>
       <c r="N39">
-        <v>5.683054066666666</v>
+        <v>5.570794266666666</v>
       </c>
       <c r="O39">
-        <v>1.079780272666667</v>
+        <v>1.058450910666667</v>
       </c>
       <c r="P39">
-        <v>4.603273794</v>
+        <v>4.512343355999999</v>
       </c>
       <c r="Q39">
-        <v>8.583273794</v>
+        <v>8.492343355999999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1044735426040959</v>
+        <v>0.1052980466846581</v>
       </c>
       <c r="T39">
-        <v>1.074626538091077</v>
+        <v>1.089727619880446</v>
       </c>
       <c r="U39">
         <v>0.07580000000000001</v>
@@ -4645,7 +4645,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.368219575091492</v>
+        <v>2.305898007325926</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4653,22 +4653,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08861602894448806</v>
+        <v>0.08869646604839566</v>
       </c>
       <c r="C40">
-        <v>82.18868937715627</v>
+        <v>80.45543229659468</v>
       </c>
       <c r="D40">
-        <v>134.5266893771563</v>
+        <v>134.2744322965947</v>
       </c>
       <c r="E40">
-        <v>-58.422</v>
+        <v>-56.941</v>
       </c>
       <c r="F40">
-        <v>56.278</v>
+        <v>57.759</v>
       </c>
       <c r="G40">
         <v>3.94</v>
@@ -4689,28 +4689,28 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M40">
-        <v>4.2658724</v>
+        <v>4.3781322</v>
       </c>
       <c r="N40">
-        <v>5.570794266666666</v>
+        <v>5.458534466666666</v>
       </c>
       <c r="O40">
-        <v>1.058450910666667</v>
+        <v>1.037121548666667</v>
       </c>
       <c r="P40">
-        <v>4.512343355999999</v>
+        <v>4.421412917999999</v>
       </c>
       <c r="Q40">
-        <v>8.492343355999999</v>
+        <v>8.401412917999998</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1052980466846581</v>
+        <v>0.1061495836858945</v>
       </c>
       <c r="T40">
-        <v>1.089727619880446</v>
+        <v>1.105323819105533</v>
       </c>
       <c r="U40">
         <v>0.07580000000000001</v>
@@ -4727,7 +4727,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.305898007325926</v>
+        <v>2.246772417394492</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4735,22 +4735,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08869646604839566</v>
+        <v>0.08877690315230326</v>
       </c>
       <c r="C41">
-        <v>80.45543229659468</v>
+        <v>78.72311948272116</v>
       </c>
       <c r="D41">
-        <v>134.2744322965947</v>
+        <v>134.0231194827212</v>
       </c>
       <c r="E41">
-        <v>-56.941</v>
+        <v>-55.46</v>
       </c>
       <c r="F41">
-        <v>57.759</v>
+        <v>59.24</v>
       </c>
       <c r="G41">
         <v>3.94</v>
@@ -4771,28 +4771,28 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M41">
-        <v>4.3781322</v>
+        <v>4.490392000000001</v>
       </c>
       <c r="N41">
-        <v>5.458534466666666</v>
+        <v>5.346274666666665</v>
       </c>
       <c r="O41">
-        <v>1.037121548666667</v>
+        <v>1.015792186666666</v>
       </c>
       <c r="P41">
-        <v>4.421412917999999</v>
+        <v>4.330482479999999</v>
       </c>
       <c r="Q41">
-        <v>8.401412917999998</v>
+        <v>8.310482479999997</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1061495836858945</v>
+        <v>0.1070295052538388</v>
       </c>
       <c r="T41">
-        <v>1.105323819105533</v>
+        <v>1.121439891638123</v>
       </c>
       <c r="U41">
         <v>0.07580000000000001</v>
@@ -4809,7 +4809,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.246772417394492</v>
+        <v>2.190603106959629</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4817,22 +4817,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08877690315230326</v>
+        <v>0.08885734025621086</v>
       </c>
       <c r="C42">
-        <v>78.72311948272116</v>
+        <v>76.99174564347089</v>
       </c>
       <c r="D42">
-        <v>134.0231194827212</v>
+        <v>133.7727456434709</v>
       </c>
       <c r="E42">
-        <v>-55.46</v>
+        <v>-53.979</v>
       </c>
       <c r="F42">
-        <v>59.24</v>
+        <v>60.721</v>
       </c>
       <c r="G42">
         <v>3.94</v>
@@ -4853,28 +4853,28 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M42">
-        <v>4.490392000000001</v>
+        <v>4.6026518</v>
       </c>
       <c r="N42">
-        <v>5.346274666666665</v>
+        <v>5.234014866666666</v>
       </c>
       <c r="O42">
-        <v>1.015792186666666</v>
+        <v>0.9944628246666665</v>
       </c>
       <c r="P42">
-        <v>4.330482479999999</v>
+        <v>4.239552042</v>
       </c>
       <c r="Q42">
-        <v>8.310482479999997</v>
+        <v>8.219552042</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1070295052538388</v>
+        <v>0.1079392546715438</v>
       </c>
       <c r="T42">
-        <v>1.121439891638123</v>
+        <v>1.13810227171419</v>
       </c>
       <c r="U42">
         <v>0.07580000000000001</v>
@@ -4891,7 +4891,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.190603106959629</v>
+        <v>2.137173762887444</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4899,22 +4899,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08885734025621086</v>
+        <v>0.08893777736011846</v>
       </c>
       <c r="C43">
-        <v>76.99174564347089</v>
+        <v>75.26130552625068</v>
       </c>
       <c r="D43">
-        <v>133.7727456434709</v>
+        <v>133.5233055262507</v>
       </c>
       <c r="E43">
-        <v>-53.979</v>
+        <v>-52.498</v>
       </c>
       <c r="F43">
-        <v>60.721</v>
+        <v>62.20200000000001</v>
       </c>
       <c r="G43">
         <v>3.94</v>
@@ -4935,28 +4935,28 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M43">
-        <v>4.6026518</v>
+        <v>4.714911600000001</v>
       </c>
       <c r="N43">
-        <v>5.234014866666666</v>
+        <v>5.121755066666665</v>
       </c>
       <c r="O43">
-        <v>0.9944628246666665</v>
+        <v>0.9731334626666664</v>
       </c>
       <c r="P43">
-        <v>4.239552042</v>
+        <v>4.148621603999999</v>
       </c>
       <c r="Q43">
-        <v>8.219552042</v>
+        <v>8.128621603999999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1079392546715438</v>
+        <v>0.1088803747588249</v>
       </c>
       <c r="T43">
-        <v>1.13810227171419</v>
+        <v>1.155339216620466</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4973,7 +4973,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.137173762887444</v>
+        <v>2.086288673294885</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4981,22 +4981,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08893777736011847</v>
+        <v>0.08901821446402608</v>
       </c>
       <c r="C44">
-        <v>75.26130552625062</v>
+        <v>73.53179391757132</v>
       </c>
       <c r="D44">
-        <v>133.5233055262506</v>
+        <v>133.2747939175713</v>
       </c>
       <c r="E44">
-        <v>-52.498</v>
+        <v>-51.017</v>
       </c>
       <c r="F44">
-        <v>62.202</v>
+        <v>63.683</v>
       </c>
       <c r="G44">
         <v>3.94</v>
@@ -5017,28 +5017,28 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M44">
-        <v>4.714911600000001</v>
+        <v>4.8271714</v>
       </c>
       <c r="N44">
-        <v>5.121755066666665</v>
+        <v>5.009495266666666</v>
       </c>
       <c r="O44">
-        <v>0.9731334626666664</v>
+        <v>0.9518041006666665</v>
       </c>
       <c r="P44">
-        <v>4.148621603999999</v>
+        <v>4.057691166</v>
       </c>
       <c r="Q44">
-        <v>8.128621603999999</v>
+        <v>8.037691165999998</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1088803747588249</v>
+        <v>0.1098545166035545</v>
       </c>
       <c r="T44">
-        <v>1.155339216620466</v>
+        <v>1.173180966611173</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -5055,7 +5055,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.086288673294885</v>
+        <v>2.037770332055469</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5063,22 +5063,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08901821446402608</v>
+        <v>0.09415953156793368</v>
       </c>
       <c r="C45">
-        <v>73.53179391757132</v>
+        <v>57.88175721948802</v>
       </c>
       <c r="D45">
-        <v>133.2747939175713</v>
+        <v>119.105757219488</v>
       </c>
       <c r="E45">
-        <v>-51.017</v>
+        <v>-49.536</v>
       </c>
       <c r="F45">
-        <v>63.683</v>
+        <v>65.164</v>
       </c>
       <c r="G45">
         <v>3.94</v>
@@ -5099,45 +5099,45 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M45">
-        <v>4.8271714</v>
+        <v>5.86476</v>
       </c>
       <c r="N45">
-        <v>5.009495266666666</v>
+        <v>3.971906666666666</v>
       </c>
       <c r="O45">
-        <v>0.9518041006666665</v>
+        <v>0.7546622666666667</v>
       </c>
       <c r="P45">
-        <v>4.057691166</v>
+        <v>3.2172444</v>
       </c>
       <c r="Q45">
-        <v>8.037691165999998</v>
+        <v>7.197244399999999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1098545166035545</v>
+        <v>0.110863449228453</v>
       </c>
       <c r="T45">
-        <v>1.173180966611173</v>
+        <v>1.191659921958692</v>
       </c>
       <c r="U45">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V45">
         <v>0.19</v>
       </c>
       <c r="W45">
-        <v>0.06139800000000001</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y45">
-        <v>2.037770332055469</v>
+        <v>1.677249651591313</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5145,22 +5145,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09415953156793368</v>
+        <v>0.09435498867184128</v>
       </c>
       <c r="C46">
-        <v>57.88175721948802</v>
+        <v>55.92129945414528</v>
       </c>
       <c r="D46">
-        <v>119.105757219488</v>
+        <v>118.6262994541453</v>
       </c>
       <c r="E46">
-        <v>-49.536</v>
+        <v>-48.05500000000001</v>
       </c>
       <c r="F46">
-        <v>65.164</v>
+        <v>66.645</v>
       </c>
       <c r="G46">
         <v>3.94</v>
@@ -5181,28 +5181,28 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M46">
-        <v>5.86476</v>
+        <v>5.998049999999999</v>
       </c>
       <c r="N46">
-        <v>3.971906666666666</v>
+        <v>3.838616666666667</v>
       </c>
       <c r="O46">
-        <v>0.7546622666666667</v>
+        <v>0.7293371666666667</v>
       </c>
       <c r="P46">
-        <v>3.2172444</v>
+        <v>3.1092795</v>
       </c>
       <c r="Q46">
-        <v>7.197244399999999</v>
+        <v>7.0892795</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.110863449228453</v>
+        <v>0.1119090703124387</v>
       </c>
       <c r="T46">
-        <v>1.191659921958692</v>
+        <v>1.210810839318847</v>
       </c>
       <c r="U46">
         <v>0.09</v>
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>1.677249651591313</v>
+        <v>1.639977437111506</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09435498867184128</v>
+        <v>0.09455044577574888</v>
       </c>
       <c r="C47">
-        <v>55.92129945414528</v>
+        <v>53.96468630703194</v>
       </c>
       <c r="D47">
-        <v>118.6262994541453</v>
+        <v>118.1506863070319</v>
       </c>
       <c r="E47">
-        <v>-48.05500000000001</v>
+        <v>-46.574</v>
       </c>
       <c r="F47">
-        <v>66.645</v>
+        <v>68.126</v>
       </c>
       <c r="G47">
         <v>3.94</v>
@@ -5263,28 +5263,28 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M47">
-        <v>5.998049999999999</v>
+        <v>6.13134</v>
       </c>
       <c r="N47">
-        <v>3.838616666666667</v>
+        <v>3.705326666666666</v>
       </c>
       <c r="O47">
-        <v>0.7293371666666667</v>
+        <v>0.7040120666666666</v>
       </c>
       <c r="P47">
-        <v>3.1092795</v>
+        <v>3.0013146</v>
       </c>
       <c r="Q47">
-        <v>7.0892795</v>
+        <v>6.981314599999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1119090703124387</v>
+        <v>0.1129934181032387</v>
       </c>
       <c r="T47">
-        <v>1.210810839318847</v>
+        <v>1.230671049914563</v>
       </c>
       <c r="U47">
         <v>0.09</v>
@@ -5301,7 +5301,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>1.639977437111506</v>
+        <v>1.604325753696038</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5309,22 +5309,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09455044577574888</v>
+        <v>0.09474590287965648</v>
       </c>
       <c r="C48">
-        <v>53.96468630703194</v>
+        <v>52.01187171966907</v>
       </c>
       <c r="D48">
-        <v>118.1506863070319</v>
+        <v>117.6788717196691</v>
       </c>
       <c r="E48">
-        <v>-46.574</v>
+        <v>-45.093</v>
       </c>
       <c r="F48">
-        <v>68.126</v>
+        <v>69.607</v>
       </c>
       <c r="G48">
         <v>3.94</v>
@@ -5345,28 +5345,28 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M48">
-        <v>6.13134</v>
+        <v>6.264629999999999</v>
       </c>
       <c r="N48">
-        <v>3.705326666666666</v>
+        <v>3.572036666666667</v>
       </c>
       <c r="O48">
-        <v>0.7040120666666666</v>
+        <v>0.6786869666666666</v>
       </c>
       <c r="P48">
-        <v>3.0013146</v>
+        <v>2.8933497</v>
       </c>
       <c r="Q48">
-        <v>6.981314599999999</v>
+        <v>6.873349699999999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1129934181032387</v>
+        <v>0.1141186846785971</v>
       </c>
       <c r="T48">
-        <v>1.230671049914563</v>
+        <v>1.251280702419552</v>
       </c>
       <c r="U48">
         <v>0.09</v>
@@ -5383,7 +5383,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>1.604325753696038</v>
+        <v>1.570191163191867</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5391,22 +5391,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09474590287965648</v>
+        <v>0.09494135998356409</v>
       </c>
       <c r="C49">
-        <v>52.01187171966907</v>
+        <v>50.06281036635822</v>
       </c>
       <c r="D49">
-        <v>117.6788717196691</v>
+        <v>117.2108103663582</v>
       </c>
       <c r="E49">
-        <v>-45.093</v>
+        <v>-43.61199999999999</v>
       </c>
       <c r="F49">
-        <v>69.607</v>
+        <v>71.08800000000001</v>
       </c>
       <c r="G49">
         <v>3.94</v>
@@ -5427,28 +5427,28 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M49">
-        <v>6.264629999999999</v>
+        <v>6.39792</v>
       </c>
       <c r="N49">
-        <v>3.572036666666667</v>
+        <v>3.438746666666666</v>
       </c>
       <c r="O49">
-        <v>0.6786869666666666</v>
+        <v>0.6533618666666665</v>
       </c>
       <c r="P49">
-        <v>2.8933497</v>
+        <v>2.785384799999999</v>
       </c>
       <c r="Q49">
-        <v>6.873349699999999</v>
+        <v>6.765384799999999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1141186846785971</v>
+        <v>0.1152872307376232</v>
       </c>
       <c r="T49">
-        <v>1.251280702419552</v>
+        <v>1.272683033867041</v>
       </c>
       <c r="U49">
         <v>0.09</v>
@@ -5465,7 +5465,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>1.570191163191867</v>
+        <v>1.537478847292036</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5473,22 +5473,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09494135998356407</v>
+        <v>0.09513681708747168</v>
       </c>
       <c r="C50">
-        <v>50.06281036635829</v>
+        <v>48.11745763966627</v>
       </c>
       <c r="D50">
-        <v>117.2108103663583</v>
+        <v>116.7464576396663</v>
       </c>
       <c r="E50">
-        <v>-43.61200000000001</v>
+        <v>-42.131</v>
       </c>
       <c r="F50">
-        <v>71.08799999999999</v>
+        <v>72.569</v>
       </c>
       <c r="G50">
         <v>3.94</v>
@@ -5509,28 +5509,28 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M50">
-        <v>6.397919999999999</v>
+        <v>6.53121</v>
       </c>
       <c r="N50">
-        <v>3.438746666666667</v>
+        <v>3.305456666666666</v>
       </c>
       <c r="O50">
-        <v>0.6533618666666667</v>
+        <v>0.6280367666666666</v>
       </c>
       <c r="P50">
-        <v>2.7853848</v>
+        <v>2.677419899999999</v>
       </c>
       <c r="Q50">
-        <v>6.7653848</v>
+        <v>6.657419899999999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1152872307376232</v>
+        <v>0.1165016021322974</v>
       </c>
       <c r="T50">
-        <v>1.27268303386704</v>
+        <v>1.294924672430116</v>
       </c>
       <c r="U50">
         <v>0.09</v>
@@ -5547,7 +5547,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>1.537478847292037</v>
+        <v>1.506101727959546</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5555,22 +5555,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09513681708747168</v>
+        <v>0.1200218838111683</v>
       </c>
       <c r="C51">
-        <v>48.11745763966627</v>
+        <v>7.493778433224989</v>
       </c>
       <c r="D51">
-        <v>116.7464576396663</v>
+        <v>77.60377843322499</v>
       </c>
       <c r="E51">
-        <v>-42.131</v>
+        <v>-40.65000000000001</v>
       </c>
       <c r="F51">
-        <v>72.569</v>
+        <v>74.05</v>
       </c>
       <c r="G51">
         <v>3.94</v>
@@ -5591,45 +5591,45 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M51">
-        <v>6.53121</v>
+        <v>10.87054</v>
       </c>
       <c r="N51">
-        <v>3.305456666666666</v>
+        <v>-1.033873333333334</v>
       </c>
       <c r="O51">
-        <v>0.6280367666666666</v>
+        <v>-0.1964359333333335</v>
       </c>
       <c r="P51">
-        <v>2.677419899999999</v>
+        <v>-0.8374374000000007</v>
       </c>
       <c r="Q51">
-        <v>6.657419899999999</v>
+        <v>3.142562599999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1165016021322974</v>
+        <v>0.1184830203794827</v>
       </c>
       <c r="T51">
-        <v>1.294924672430116</v>
+        <v>1.331215043472662</v>
       </c>
       <c r="U51">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V51">
-        <v>0.19</v>
+        <v>0.1719295146944555</v>
       </c>
       <c r="W51">
-        <v>0.07290000000000001</v>
+        <v>0.1215607472428539</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y51">
-        <v>1.506101727959546</v>
+        <v>0.9048921826023975</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5637,22 +5637,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1200218838111683</v>
+        <v>0.1210318838111683</v>
       </c>
       <c r="C52">
-        <v>7.493778433224989</v>
+        <v>4.970935370856779</v>
       </c>
       <c r="D52">
-        <v>77.60377843322499</v>
+        <v>76.56193537085677</v>
       </c>
       <c r="E52">
-        <v>-40.65000000000001</v>
+        <v>-39.16900000000001</v>
       </c>
       <c r="F52">
-        <v>74.05</v>
+        <v>75.53099999999999</v>
       </c>
       <c r="G52">
         <v>3.94</v>
@@ -5673,37 +5673,37 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M52">
-        <v>10.87054</v>
+        <v>11.0879508</v>
       </c>
       <c r="N52">
-        <v>-1.033873333333334</v>
+        <v>-1.251284133333334</v>
       </c>
       <c r="O52">
-        <v>-0.1964359333333335</v>
+        <v>-0.2377439853333334</v>
       </c>
       <c r="P52">
-        <v>-0.8374374000000007</v>
+        <v>-1.013540148</v>
       </c>
       <c r="Q52">
-        <v>3.142562599999999</v>
+        <v>2.966459851999999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1184830203794827</v>
+        <v>0.1199663473260028</v>
       </c>
       <c r="T52">
-        <v>1.331215043472662</v>
+        <v>1.358382697421084</v>
       </c>
       <c r="U52">
         <v>0.1468</v>
       </c>
       <c r="V52">
-        <v>0.1719295146944555</v>
+        <v>0.1685583477396623</v>
       </c>
       <c r="W52">
-        <v>0.1215607472428539</v>
+        <v>0.1220556345518176</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.9048921826023975</v>
+        <v>0.8871491986298015</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5719,22 +5719,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1210318838111683</v>
+        <v>0.1220418838111683</v>
       </c>
       <c r="C53">
-        <v>4.970935370856779</v>
+        <v>2.475695548083138</v>
       </c>
       <c r="D53">
-        <v>76.56193537085677</v>
+        <v>75.54769554808314</v>
       </c>
       <c r="E53">
-        <v>-39.16900000000001</v>
+        <v>-37.688</v>
       </c>
       <c r="F53">
-        <v>75.53099999999999</v>
+        <v>77.012</v>
       </c>
       <c r="G53">
         <v>3.94</v>
@@ -5755,37 +5755,37 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M53">
-        <v>11.0879508</v>
+        <v>11.3053616</v>
       </c>
       <c r="N53">
-        <v>-1.251284133333334</v>
+        <v>-1.468694933333335</v>
       </c>
       <c r="O53">
-        <v>-0.2377439853333334</v>
+        <v>-0.2790520373333337</v>
       </c>
       <c r="P53">
-        <v>-1.013540148</v>
+        <v>-1.189642896000002</v>
       </c>
       <c r="Q53">
-        <v>2.966459851999999</v>
+        <v>2.790357103999998</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1199663473260028</v>
+        <v>0.1215114795619612</v>
       </c>
       <c r="T53">
-        <v>1.358382697421084</v>
+        <v>1.38668233695069</v>
       </c>
       <c r="U53">
         <v>0.1468</v>
       </c>
       <c r="V53">
-        <v>0.1685583477396623</v>
+        <v>0.1653168410523611</v>
       </c>
       <c r="W53">
-        <v>0.1220556345518176</v>
+        <v>0.1225314877335134</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5793,7 +5793,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.8871491986298015</v>
+        <v>0.8700886371176898</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5801,22 +5801,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1220418838111683</v>
+        <v>0.1230518838111684</v>
       </c>
       <c r="C54">
-        <v>2.475695548083138</v>
+        <v>0.006976301131473406</v>
       </c>
       <c r="D54">
-        <v>75.54769554808314</v>
+        <v>74.55997630113147</v>
       </c>
       <c r="E54">
-        <v>-37.688</v>
+        <v>-36.20700000000001</v>
       </c>
       <c r="F54">
-        <v>77.012</v>
+        <v>78.49299999999999</v>
       </c>
       <c r="G54">
         <v>3.94</v>
@@ -5837,37 +5837,37 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M54">
-        <v>11.3053616</v>
+        <v>11.5227724</v>
       </c>
       <c r="N54">
-        <v>-1.468694933333335</v>
+        <v>-1.686105733333335</v>
       </c>
       <c r="O54">
-        <v>-0.2790520373333337</v>
+        <v>-0.3203600893333337</v>
       </c>
       <c r="P54">
-        <v>-1.189642896000002</v>
+        <v>-1.365745644000001</v>
       </c>
       <c r="Q54">
-        <v>2.790357103999998</v>
+        <v>2.614254355999998</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1215114795619612</v>
+        <v>0.1231223621058327</v>
       </c>
       <c r="T54">
-        <v>1.38668233695069</v>
+        <v>1.416186216460279</v>
       </c>
       <c r="U54">
         <v>0.1468</v>
       </c>
       <c r="V54">
-        <v>0.1653168410523611</v>
+        <v>0.1621976553721279</v>
       </c>
       <c r="W54">
-        <v>0.1225314877335134</v>
+        <v>0.1229893841913716</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5875,7 +5875,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.8700886371176898</v>
+        <v>0.8536718703796202</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5883,22 +5883,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1230518838111684</v>
+        <v>0.1240618838111683</v>
       </c>
       <c r="C55">
-        <v>0.006976301131473406</v>
+        <v>-2.436249144985311</v>
       </c>
       <c r="D55">
-        <v>74.55997630113147</v>
+        <v>73.5977508550147</v>
       </c>
       <c r="E55">
-        <v>-36.20700000000001</v>
+        <v>-34.726</v>
       </c>
       <c r="F55">
-        <v>78.49299999999999</v>
+        <v>79.974</v>
       </c>
       <c r="G55">
         <v>3.94</v>
@@ -5919,37 +5919,37 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M55">
-        <v>11.5227724</v>
+        <v>11.7401832</v>
       </c>
       <c r="N55">
-        <v>-1.686105733333335</v>
+        <v>-1.903516533333336</v>
       </c>
       <c r="O55">
-        <v>-0.3203600893333337</v>
+        <v>-0.3616681413333339</v>
       </c>
       <c r="P55">
-        <v>-1.365745644000001</v>
+        <v>-1.541848392000003</v>
       </c>
       <c r="Q55">
-        <v>2.614254355999998</v>
+        <v>2.438151607999997</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1231223621058327</v>
+        <v>0.1248032830211769</v>
       </c>
       <c r="T55">
-        <v>1.416186216460279</v>
+        <v>1.446972873339851</v>
       </c>
       <c r="U55">
         <v>0.1468</v>
       </c>
       <c r="V55">
-        <v>0.1621976553721279</v>
+        <v>0.1591939950874588</v>
       </c>
       <c r="W55">
-        <v>0.1229893841913716</v>
+        <v>0.1234303215211611</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.8536718703796202</v>
+        <v>0.8378631320392568</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5965,22 +5965,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1240618838111683</v>
+        <v>0.1250718838111683</v>
       </c>
       <c r="C56">
-        <v>-2.436249144985311</v>
+        <v>-4.854955236853073</v>
       </c>
       <c r="D56">
-        <v>73.5977508550147</v>
+        <v>72.66004476314693</v>
       </c>
       <c r="E56">
-        <v>-34.726</v>
+        <v>-33.245</v>
       </c>
       <c r="F56">
-        <v>79.974</v>
+        <v>81.455</v>
       </c>
       <c r="G56">
         <v>3.94</v>
@@ -6001,37 +6001,37 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M56">
-        <v>11.7401832</v>
+        <v>11.957594</v>
       </c>
       <c r="N56">
-        <v>-1.903516533333336</v>
+        <v>-2.120927333333334</v>
       </c>
       <c r="O56">
-        <v>-0.3616681413333339</v>
+        <v>-0.4029761933333335</v>
       </c>
       <c r="P56">
-        <v>-1.541848392000003</v>
+        <v>-1.717951140000001</v>
       </c>
       <c r="Q56">
-        <v>2.438151607999997</v>
+        <v>2.262048859999999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1248032830211769</v>
+        <v>0.1265589115327586</v>
       </c>
       <c r="T56">
-        <v>1.446972873339851</v>
+        <v>1.479127826080736</v>
       </c>
       <c r="U56">
         <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.1591939950874588</v>
+        <v>0.1562995588131414</v>
       </c>
       <c r="W56">
-        <v>0.1234303215211611</v>
+        <v>0.1238552247662309</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.8378631320392568</v>
+        <v>0.8226292569112704</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6047,22 +6047,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1250718838111683</v>
+        <v>0.1260818838111684</v>
       </c>
       <c r="C57">
-        <v>-4.854955236853073</v>
+        <v>-7.250067384288386</v>
       </c>
       <c r="D57">
-        <v>72.66004476314693</v>
+        <v>71.74593261571162</v>
       </c>
       <c r="E57">
-        <v>-33.245</v>
+        <v>-31.764</v>
       </c>
       <c r="F57">
-        <v>81.455</v>
+        <v>82.93600000000001</v>
       </c>
       <c r="G57">
         <v>3.94</v>
@@ -6083,37 +6083,37 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M57">
-        <v>11.957594</v>
+        <v>12.1750048</v>
       </c>
       <c r="N57">
-        <v>-2.120927333333334</v>
+        <v>-2.338338133333336</v>
       </c>
       <c r="O57">
-        <v>-0.4029761933333335</v>
+        <v>-0.4442842453333338</v>
       </c>
       <c r="P57">
-        <v>-1.717951140000001</v>
+        <v>-1.894053888000002</v>
       </c>
       <c r="Q57">
-        <v>2.262048859999999</v>
+        <v>2.085946111999998</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1265589115327586</v>
+        <v>0.1283943413403213</v>
       </c>
       <c r="T57">
-        <v>1.479127826080736</v>
+        <v>1.512744367582571</v>
       </c>
       <c r="U57">
         <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.1562995588131414</v>
+        <v>0.1535084952629067</v>
       </c>
       <c r="W57">
-        <v>0.1238552247662309</v>
+        <v>0.1242649528954053</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.8226292569112704</v>
+        <v>0.8079394487521405</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6129,22 +6129,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1260818838111684</v>
+        <v>0.1587910425538871</v>
       </c>
       <c r="C58">
-        <v>-7.250067384288386</v>
+        <v>-29.50040490015838</v>
       </c>
       <c r="D58">
-        <v>71.74593261571162</v>
+        <v>50.97659509984162</v>
       </c>
       <c r="E58">
-        <v>-31.764</v>
+        <v>-30.283</v>
       </c>
       <c r="F58">
-        <v>82.93600000000001</v>
+        <v>84.417</v>
       </c>
       <c r="G58">
         <v>3.94</v>
@@ -6165,45 +6165,45 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M58">
-        <v>12.1750048</v>
+        <v>16.9509336</v>
       </c>
       <c r="N58">
-        <v>-2.338338133333336</v>
+        <v>-7.114266933333337</v>
       </c>
       <c r="O58">
-        <v>-0.4442842453333338</v>
+        <v>-1.351710717333334</v>
       </c>
       <c r="P58">
-        <v>-1.894053888000002</v>
+        <v>-5.762556216000003</v>
       </c>
       <c r="Q58">
-        <v>2.085946111999998</v>
+        <v>-1.782556216000003</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1283943413403213</v>
+        <v>0.1324527184475816</v>
       </c>
       <c r="T58">
-        <v>1.512744367582571</v>
+        <v>1.587074969545215</v>
       </c>
       <c r="U58">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.1535084952629067</v>
+        <v>0.110257447216162</v>
       </c>
       <c r="W58">
-        <v>0.1242649528954053</v>
+        <v>0.1786603045989947</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y58">
-        <v>0.8079394487521405</v>
+        <v>0.5803023537692735</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6211,22 +6211,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1587910425538871</v>
+        <v>0.1603410425538871</v>
       </c>
       <c r="C59">
-        <v>-29.50040490015838</v>
+        <v>-31.67123380901945</v>
       </c>
       <c r="D59">
-        <v>50.97659509984162</v>
+        <v>50.28676619098056</v>
       </c>
       <c r="E59">
-        <v>-30.283</v>
+        <v>-28.80199999999999</v>
       </c>
       <c r="F59">
-        <v>84.417</v>
+        <v>85.89800000000001</v>
       </c>
       <c r="G59">
         <v>3.94</v>
@@ -6247,37 +6247,37 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M59">
-        <v>16.9509336</v>
+        <v>17.2483184</v>
       </c>
       <c r="N59">
-        <v>-7.114266933333337</v>
+        <v>-7.411651733333336</v>
       </c>
       <c r="O59">
-        <v>-1.351710717333334</v>
+        <v>-1.408213829333334</v>
       </c>
       <c r="P59">
-        <v>-5.762556216000003</v>
+        <v>-6.003437904000002</v>
       </c>
       <c r="Q59">
-        <v>-1.782556216000003</v>
+        <v>-2.023437904000002</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1324527184475816</v>
+        <v>0.1345158784106193</v>
       </c>
       <c r="T59">
-        <v>1.587074969545215</v>
+        <v>1.624862468820101</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.110257447216162</v>
+        <v>0.1083564567469178</v>
       </c>
       <c r="W59">
-        <v>0.1786603045989947</v>
+        <v>0.1790420234852189</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.5803023537692735</v>
+        <v>0.5702971407732516</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.160341042553887</v>
+        <v>0.1618910425538871</v>
       </c>
       <c r="C60">
-        <v>-31.67123380901941</v>
+        <v>-33.82364209239185</v>
       </c>
       <c r="D60">
-        <v>50.28676619098059</v>
+        <v>49.61535790760814</v>
       </c>
       <c r="E60">
-        <v>-28.80200000000001</v>
+        <v>-27.32100000000001</v>
       </c>
       <c r="F60">
-        <v>85.898</v>
+        <v>87.37899999999999</v>
       </c>
       <c r="G60">
         <v>3.94</v>
@@ -6329,37 +6329,37 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M60">
-        <v>17.2483184</v>
+        <v>17.5457032</v>
       </c>
       <c r="N60">
-        <v>-7.411651733333333</v>
+        <v>-7.709036533333332</v>
       </c>
       <c r="O60">
-        <v>-1.408213829333333</v>
+        <v>-1.464716941333333</v>
       </c>
       <c r="P60">
-        <v>-6.003437903999999</v>
+        <v>-6.244319591999999</v>
       </c>
       <c r="Q60">
-        <v>-2.023437904</v>
+        <v>-2.264319592</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1345158784106193</v>
+        <v>0.1366796803230734</v>
       </c>
       <c r="T60">
-        <v>1.6248624688201</v>
+        <v>1.664493260742542</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.1083564567469178</v>
+        <v>0.1065199066325633</v>
       </c>
       <c r="W60">
-        <v>0.1790420234852189</v>
+        <v>0.1794108027481813</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.5702971407732517</v>
+        <v>0.5606310875398067</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6375,22 +6375,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1618910425538871</v>
+        <v>0.1634410425538871</v>
       </c>
       <c r="C61">
-        <v>-33.82364209239185</v>
+        <v>-35.95835786273251</v>
       </c>
       <c r="D61">
-        <v>49.61535790760814</v>
+        <v>48.9616421372675</v>
       </c>
       <c r="E61">
-        <v>-27.32100000000001</v>
+        <v>-25.84</v>
       </c>
       <c r="F61">
-        <v>87.37899999999999</v>
+        <v>88.86</v>
       </c>
       <c r="G61">
         <v>3.94</v>
@@ -6411,37 +6411,37 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M61">
-        <v>17.5457032</v>
+        <v>17.843088</v>
       </c>
       <c r="N61">
-        <v>-7.709036533333332</v>
+        <v>-8.006421333333336</v>
       </c>
       <c r="O61">
-        <v>-1.464716941333333</v>
+        <v>-1.521220053333334</v>
       </c>
       <c r="P61">
-        <v>-6.244319591999999</v>
+        <v>-6.485201280000002</v>
       </c>
       <c r="Q61">
-        <v>-2.264319592</v>
+        <v>-2.505201280000002</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1366796803230734</v>
+        <v>0.1389516723311502</v>
       </c>
       <c r="T61">
-        <v>1.664493260742542</v>
+        <v>1.706105592261105</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.1065199066325633</v>
+        <v>0.1047445748553539</v>
       </c>
       <c r="W61">
-        <v>0.1794108027481813</v>
+        <v>0.1797672893690449</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.5606310875398067</v>
+        <v>0.5512872360808099</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6457,22 +6457,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1634410425538871</v>
+        <v>0.1649910425538871</v>
       </c>
       <c r="C62">
-        <v>-35.95835786273251</v>
+        <v>-38.07607135803107</v>
       </c>
       <c r="D62">
-        <v>48.9616421372675</v>
+        <v>48.32492864196893</v>
       </c>
       <c r="E62">
-        <v>-25.84</v>
+        <v>-24.35900000000001</v>
       </c>
       <c r="F62">
-        <v>88.86</v>
+        <v>90.34099999999999</v>
       </c>
       <c r="G62">
         <v>3.94</v>
@@ -6493,37 +6493,37 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M62">
-        <v>17.843088</v>
+        <v>18.1404728</v>
       </c>
       <c r="N62">
-        <v>-8.006421333333336</v>
+        <v>-8.303806133333332</v>
       </c>
       <c r="O62">
-        <v>-1.521220053333334</v>
+        <v>-1.577723165333333</v>
       </c>
       <c r="P62">
-        <v>-6.485201280000002</v>
+        <v>-6.726082967999998</v>
       </c>
       <c r="Q62">
-        <v>-2.505201280000002</v>
+        <v>-2.746082967999999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1389516723311502</v>
+        <v>0.1413401767498977</v>
       </c>
       <c r="T62">
-        <v>1.706105592261105</v>
+        <v>1.74985188949857</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.1047445748553539</v>
+        <v>0.1030274506773973</v>
       </c>
       <c r="W62">
-        <v>0.1797672893690449</v>
+        <v>0.1801120879039786</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.5512872360808099</v>
+        <v>0.5422497404073541</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6539,22 +6539,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1649910425538871</v>
+        <v>0.1665410425538871</v>
       </c>
       <c r="C63">
-        <v>-38.07607135803107</v>
+        <v>-40.17743737285674</v>
       </c>
       <c r="D63">
-        <v>48.32492864196893</v>
+        <v>47.70456262714326</v>
       </c>
       <c r="E63">
-        <v>-24.35900000000001</v>
+        <v>-22.878</v>
       </c>
       <c r="F63">
-        <v>90.34099999999999</v>
+        <v>91.822</v>
       </c>
       <c r="G63">
         <v>3.94</v>
@@ -6575,37 +6575,37 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M63">
-        <v>18.1404728</v>
+        <v>18.4378576</v>
       </c>
       <c r="N63">
-        <v>-8.303806133333332</v>
+        <v>-8.601190933333335</v>
       </c>
       <c r="O63">
-        <v>-1.577723165333333</v>
+        <v>-1.634226277333334</v>
       </c>
       <c r="P63">
-        <v>-6.726082967999998</v>
+        <v>-6.966964656000002</v>
       </c>
       <c r="Q63">
-        <v>-2.746082967999999</v>
+        <v>-2.986964656000002</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1413401767498977</v>
+        <v>0.1438543919275266</v>
       </c>
       <c r="T63">
-        <v>1.74985188949857</v>
+        <v>1.795900623432743</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.1030274506773973</v>
+        <v>0.1013657176019554</v>
       </c>
       <c r="W63">
-        <v>0.1801120879039786</v>
+        <v>0.1804457639055274</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.5422497404073541</v>
+        <v>0.5335037768523967</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6621,22 +6621,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1665410425538871</v>
+        <v>0.1680910425538871</v>
       </c>
       <c r="C64">
-        <v>-40.17743737285674</v>
+        <v>-42.2630775045286</v>
       </c>
       <c r="D64">
-        <v>47.70456262714326</v>
+        <v>47.0999224954714</v>
       </c>
       <c r="E64">
-        <v>-22.878</v>
+        <v>-21.39700000000001</v>
       </c>
       <c r="F64">
-        <v>91.822</v>
+        <v>93.303</v>
       </c>
       <c r="G64">
         <v>3.94</v>
@@ -6657,37 +6657,37 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M64">
-        <v>18.4378576</v>
+        <v>18.7352424</v>
       </c>
       <c r="N64">
-        <v>-8.601190933333335</v>
+        <v>-8.898575733333335</v>
       </c>
       <c r="O64">
-        <v>-1.634226277333334</v>
+        <v>-1.690729389333333</v>
       </c>
       <c r="P64">
-        <v>-6.966964656000002</v>
+        <v>-7.207846344000001</v>
       </c>
       <c r="Q64">
-        <v>-2.986964656000002</v>
+        <v>-3.227846344000001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1438543919275266</v>
+        <v>0.1465045106282706</v>
       </c>
       <c r="T64">
-        <v>1.795900623432743</v>
+        <v>1.844438478120114</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.1013657176019554</v>
+        <v>0.09975673795747989</v>
       </c>
       <c r="W64">
-        <v>0.1804457639055274</v>
+        <v>0.1807688470181381</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.5335037768523967</v>
+        <v>0.5250354629341046</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6703,22 +6703,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1680910425538871</v>
+        <v>0.1696410425538871</v>
       </c>
       <c r="C65">
-        <v>-42.2630775045286</v>
+        <v>-44.33358223060689</v>
       </c>
       <c r="D65">
-        <v>47.0999224954714</v>
+        <v>46.5104177693931</v>
       </c>
       <c r="E65">
-        <v>-21.39700000000001</v>
+        <v>-19.91600000000001</v>
       </c>
       <c r="F65">
-        <v>93.303</v>
+        <v>94.78399999999999</v>
       </c>
       <c r="G65">
         <v>3.94</v>
@@ -6739,37 +6739,37 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M65">
-        <v>18.7352424</v>
+        <v>19.0326272</v>
       </c>
       <c r="N65">
-        <v>-8.898575733333335</v>
+        <v>-9.195960533333334</v>
       </c>
       <c r="O65">
-        <v>-1.690729389333333</v>
+        <v>-1.747232501333334</v>
       </c>
       <c r="P65">
-        <v>-7.207846344000001</v>
+        <v>-7.448728032000001</v>
       </c>
       <c r="Q65">
-        <v>-3.227846344000001</v>
+        <v>-3.468728032000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1465045106282706</v>
+        <v>0.1493018581457225</v>
       </c>
       <c r="T65">
-        <v>1.844438478120114</v>
+        <v>1.895672880290117</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.09975673795747989</v>
+        <v>0.09819803892689426</v>
       </c>
       <c r="W65">
-        <v>0.1807688470181381</v>
+        <v>0.1810818337834796</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.5250354629341046</v>
+        <v>0.5168317838257592</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6785,22 +6785,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1696410425538871</v>
+        <v>0.1711910425538871</v>
       </c>
       <c r="C66">
-        <v>-44.33358223060689</v>
+        <v>-46.38951283230104</v>
       </c>
       <c r="D66">
-        <v>46.5104177693931</v>
+        <v>45.93548716769897</v>
       </c>
       <c r="E66">
-        <v>-19.91600000000001</v>
+        <v>-18.435</v>
       </c>
       <c r="F66">
-        <v>94.78399999999999</v>
+        <v>96.265</v>
       </c>
       <c r="G66">
         <v>3.94</v>
@@ -6821,37 +6821,37 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M66">
-        <v>19.0326272</v>
+        <v>19.330012</v>
       </c>
       <c r="N66">
-        <v>-9.195960533333334</v>
+        <v>-9.493345333333334</v>
       </c>
       <c r="O66">
-        <v>-1.747232501333334</v>
+        <v>-1.803735613333334</v>
       </c>
       <c r="P66">
-        <v>-7.448728032000001</v>
+        <v>-7.68960972</v>
       </c>
       <c r="Q66">
-        <v>-3.468728032000001</v>
+        <v>-3.70960972</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1493018581457225</v>
+        <v>0.1522590540927432</v>
       </c>
       <c r="T66">
-        <v>1.895672880290117</v>
+        <v>1.949834962584121</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.09819803892689426</v>
+        <v>0.0966872998664805</v>
       </c>
       <c r="W66">
-        <v>0.1810818337834796</v>
+        <v>0.1813851901868107</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.5168317838257592</v>
+        <v>0.5088805256130553</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6867,22 +6867,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1711910425538871</v>
+        <v>0.1727410425538871</v>
       </c>
       <c r="C67">
-        <v>-46.38951283230104</v>
+        <v>-48.43140317696405</v>
       </c>
       <c r="D67">
-        <v>45.93548716769897</v>
+        <v>45.37459682303594</v>
       </c>
       <c r="E67">
-        <v>-18.435</v>
+        <v>-16.95400000000001</v>
       </c>
       <c r="F67">
-        <v>96.265</v>
+        <v>97.746</v>
       </c>
       <c r="G67">
         <v>3.94</v>
@@ -6903,37 +6903,37 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M67">
-        <v>19.330012</v>
+        <v>19.6273968</v>
       </c>
       <c r="N67">
-        <v>-9.493345333333334</v>
+        <v>-9.790730133333334</v>
       </c>
       <c r="O67">
-        <v>-1.803735613333334</v>
+        <v>-1.860238725333333</v>
       </c>
       <c r="P67">
-        <v>-7.68960972</v>
+        <v>-7.930491408</v>
       </c>
       <c r="Q67">
-        <v>-3.70960972</v>
+        <v>-3.950491408</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1522590540927432</v>
+        <v>0.1553902027425297</v>
       </c>
       <c r="T67">
-        <v>1.949834962584121</v>
+        <v>2.007183049718948</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.0966872998664805</v>
+        <v>0.09522234077759444</v>
       </c>
       <c r="W67">
-        <v>0.1813851901868107</v>
+        <v>0.1816793539718591</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6941,7 +6941,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5088805256130553</v>
+        <v>0.5011702146189181</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6949,22 +6949,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1727410425538871</v>
+        <v>0.1981119342087805</v>
       </c>
       <c r="C68">
-        <v>-48.43140317696405</v>
+        <v>-57.4705369887488</v>
       </c>
       <c r="D68">
-        <v>45.37459682303594</v>
+        <v>37.81646301125121</v>
       </c>
       <c r="E68">
-        <v>-16.95400000000001</v>
+        <v>-15.473</v>
       </c>
       <c r="F68">
-        <v>97.746</v>
+        <v>99.227</v>
       </c>
       <c r="G68">
         <v>3.94</v>
@@ -6985,45 +6985,45 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M68">
-        <v>19.6273968</v>
+        <v>23.3977266</v>
       </c>
       <c r="N68">
-        <v>-9.790730133333334</v>
+        <v>-13.56105993333334</v>
       </c>
       <c r="O68">
-        <v>-1.860238725333333</v>
+        <v>-2.576601387333334</v>
       </c>
       <c r="P68">
-        <v>-7.930491408</v>
+        <v>-10.984458546</v>
       </c>
       <c r="Q68">
-        <v>-3.950491408</v>
+        <v>-7.004458546000003</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1553902027425297</v>
+        <v>0.1598350320828895</v>
       </c>
       <c r="T68">
-        <v>2.007183049718948</v>
+        <v>2.088591660047226</v>
       </c>
       <c r="U68">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.09522234077759444</v>
+        <v>0.07987813083800485</v>
       </c>
       <c r="W68">
-        <v>0.1816793539718591</v>
+        <v>0.2169647367483984</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y68">
-        <v>0.5011702146189181</v>
+        <v>0.4204112149368676</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7031,22 +7031,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1981119342087805</v>
+        <v>0.2000119342087805</v>
       </c>
       <c r="C69">
-        <v>-57.4705369887488</v>
+        <v>-59.41746253523796</v>
       </c>
       <c r="D69">
-        <v>37.81646301125121</v>
+        <v>37.35053746476204</v>
       </c>
       <c r="E69">
-        <v>-15.473</v>
+        <v>-13.992</v>
       </c>
       <c r="F69">
-        <v>99.227</v>
+        <v>100.708</v>
       </c>
       <c r="G69">
         <v>3.94</v>
@@ -7067,37 +7067,37 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M69">
-        <v>23.3977266</v>
+        <v>23.7469464</v>
       </c>
       <c r="N69">
-        <v>-13.56105993333334</v>
+        <v>-13.91027973333334</v>
       </c>
       <c r="O69">
-        <v>-2.576601387333334</v>
+        <v>-2.642953149333334</v>
       </c>
       <c r="P69">
-        <v>-10.984458546</v>
+        <v>-11.267326584</v>
       </c>
       <c r="Q69">
-        <v>-7.004458546000003</v>
+        <v>-7.287326584000003</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1598350320828895</v>
+        <v>0.1633986268354798</v>
       </c>
       <c r="T69">
-        <v>2.088591660047226</v>
+        <v>2.153860149423702</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.07987813083800485</v>
+        <v>0.07870345244332831</v>
       </c>
       <c r="W69">
-        <v>0.2169647367483984</v>
+        <v>0.2172417259138632</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.4204112149368676</v>
+        <v>0.414228697070149</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7113,22 +7113,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2000119342087805</v>
+        <v>0.2019119342087805</v>
       </c>
       <c r="C70">
-        <v>-59.41746253523796</v>
+        <v>-61.3530467509978</v>
       </c>
       <c r="D70">
-        <v>37.35053746476204</v>
+        <v>36.89595324900221</v>
       </c>
       <c r="E70">
-        <v>-13.992</v>
+        <v>-12.511</v>
       </c>
       <c r="F70">
-        <v>100.708</v>
+        <v>102.189</v>
       </c>
       <c r="G70">
         <v>3.94</v>
@@ -7149,37 +7149,37 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M70">
-        <v>23.7469464</v>
+        <v>24.0961662</v>
       </c>
       <c r="N70">
-        <v>-13.91027973333334</v>
+        <v>-14.25949953333334</v>
       </c>
       <c r="O70">
-        <v>-2.642953149333334</v>
+        <v>-2.709304911333334</v>
       </c>
       <c r="P70">
-        <v>-11.267326584</v>
+        <v>-11.550194622</v>
       </c>
       <c r="Q70">
-        <v>-7.287326584000003</v>
+        <v>-7.570194622000003</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1633986268354798</v>
+        <v>0.1671921309269469</v>
       </c>
       <c r="T70">
-        <v>2.153860149423702</v>
+        <v>2.223339509082531</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.07870345244332831</v>
+        <v>0.07756282269777283</v>
       </c>
       <c r="W70">
-        <v>0.2172417259138632</v>
+        <v>0.2175106864078652</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.414228697070149</v>
+        <v>0.408225382619857</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7195,22 +7195,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2019119342087805</v>
+        <v>0.2038119342087805</v>
       </c>
       <c r="C71">
-        <v>-61.3530467509978</v>
+        <v>-63.2776987543995</v>
       </c>
       <c r="D71">
-        <v>36.89595324900221</v>
+        <v>36.4523012456005</v>
       </c>
       <c r="E71">
-        <v>-12.511</v>
+        <v>-11.03</v>
       </c>
       <c r="F71">
-        <v>102.189</v>
+        <v>103.67</v>
       </c>
       <c r="G71">
         <v>3.94</v>
@@ -7231,37 +7231,37 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M71">
-        <v>24.0961662</v>
+        <v>24.445386</v>
       </c>
       <c r="N71">
-        <v>-14.25949953333334</v>
+        <v>-14.60871933333334</v>
       </c>
       <c r="O71">
-        <v>-2.709304911333334</v>
+        <v>-2.775656673333334</v>
       </c>
       <c r="P71">
-        <v>-11.550194622</v>
+        <v>-11.83306266</v>
       </c>
       <c r="Q71">
-        <v>-7.570194622000003</v>
+        <v>-7.853062660000004</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1671921309269469</v>
+        <v>0.1712385352911785</v>
       </c>
       <c r="T71">
-        <v>2.223339509082531</v>
+        <v>2.297450826051949</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.07756282269777283</v>
+        <v>0.07645478237351894</v>
       </c>
       <c r="W71">
-        <v>0.2175106864078652</v>
+        <v>0.2177719623163243</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.408225382619857</v>
+        <v>0.4023935914395733</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7277,22 +7277,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2038119342087805</v>
+        <v>0.2057119342087805</v>
       </c>
       <c r="C72">
-        <v>-63.2776987543995</v>
+        <v>-65.19180821998958</v>
       </c>
       <c r="D72">
-        <v>36.4523012456005</v>
+        <v>36.01919178001044</v>
       </c>
       <c r="E72">
-        <v>-11.03</v>
+        <v>-9.548999999999992</v>
       </c>
       <c r="F72">
-        <v>103.67</v>
+        <v>105.151</v>
       </c>
       <c r="G72">
         <v>3.94</v>
@@ -7313,37 +7313,37 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M72">
-        <v>24.445386</v>
+        <v>24.7946058</v>
       </c>
       <c r="N72">
-        <v>-14.60871933333334</v>
+        <v>-14.95793913333334</v>
       </c>
       <c r="O72">
-        <v>-2.775656673333334</v>
+        <v>-2.842008435333334</v>
       </c>
       <c r="P72">
-        <v>-11.83306266</v>
+        <v>-12.115930698</v>
       </c>
       <c r="Q72">
-        <v>-7.853062660000004</v>
+        <v>-8.135930698000003</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1712385352911785</v>
+        <v>0.175564002025357</v>
       </c>
       <c r="T72">
-        <v>2.297450826051949</v>
+        <v>2.376673268329602</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.07645478237351894</v>
+        <v>0.07537795445276514</v>
       </c>
       <c r="W72">
-        <v>0.2177719623163243</v>
+        <v>0.218025878340038</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.4023935914395733</v>
+        <v>0.3967260760671849</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7359,22 +7359,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2057119342087805</v>
+        <v>0.2076119342087805</v>
       </c>
       <c r="C73">
-        <v>-65.19180821998955</v>
+        <v>-67.09574652003928</v>
       </c>
       <c r="D73">
-        <v>36.01919178001044</v>
+        <v>35.59625347996071</v>
       </c>
       <c r="E73">
-        <v>-9.549000000000007</v>
+        <v>-8.068000000000012</v>
       </c>
       <c r="F73">
-        <v>105.151</v>
+        <v>106.632</v>
       </c>
       <c r="G73">
         <v>3.94</v>
@@ -7395,37 +7395,37 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M73">
-        <v>24.7946058</v>
+        <v>25.1438256</v>
       </c>
       <c r="N73">
-        <v>-14.95793913333333</v>
+        <v>-15.30715893333333</v>
       </c>
       <c r="O73">
-        <v>-2.842008435333333</v>
+        <v>-2.908360197333333</v>
       </c>
       <c r="P73">
-        <v>-12.115930698</v>
+        <v>-12.398798736</v>
       </c>
       <c r="Q73">
-        <v>-8.135930697999999</v>
+        <v>-8.418798735999999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.175564002025357</v>
+        <v>0.1801984306691197</v>
       </c>
       <c r="T73">
-        <v>2.376673268329601</v>
+        <v>2.46155445648423</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.07537795445276516</v>
+        <v>0.07433103841869897</v>
       </c>
       <c r="W73">
-        <v>0.218025878340038</v>
+        <v>0.2182727411408708</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.396726076067185</v>
+        <v>0.391215991677363</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7441,22 +7441,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2076119342087805</v>
+        <v>0.2095119342087805</v>
       </c>
       <c r="C74">
-        <v>-67.09574652003928</v>
+        <v>-68.98986778660299</v>
       </c>
       <c r="D74">
-        <v>35.59625347996071</v>
+        <v>35.18313221339701</v>
       </c>
       <c r="E74">
-        <v>-8.068000000000012</v>
+        <v>-6.587000000000003</v>
       </c>
       <c r="F74">
-        <v>106.632</v>
+        <v>108.113</v>
       </c>
       <c r="G74">
         <v>3.94</v>
@@ -7477,37 +7477,37 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M74">
-        <v>25.1438256</v>
+        <v>25.4930454</v>
       </c>
       <c r="N74">
-        <v>-15.30715893333333</v>
+        <v>-15.65637873333333</v>
       </c>
       <c r="O74">
-        <v>-2.908360197333333</v>
+        <v>-2.974711959333333</v>
       </c>
       <c r="P74">
-        <v>-12.398798736</v>
+        <v>-12.681666774</v>
       </c>
       <c r="Q74">
-        <v>-8.418798735999999</v>
+        <v>-8.701666774</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1801984306691197</v>
+        <v>0.1851761503235315</v>
       </c>
       <c r="T74">
-        <v>2.46155445648423</v>
+        <v>2.552723140057719</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.07433103841869897</v>
+        <v>0.0733128050157031</v>
       </c>
       <c r="W74">
-        <v>0.2182727411408708</v>
+        <v>0.2185128405772972</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.391215991677363</v>
+        <v>0.3858568685037005</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7523,22 +7523,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2095119342087805</v>
+        <v>0.2114119342087805</v>
       </c>
       <c r="C75">
-        <v>-68.98986778660299</v>
+        <v>-70.87450990046891</v>
       </c>
       <c r="D75">
-        <v>35.18313221339701</v>
+        <v>34.77949009953109</v>
       </c>
       <c r="E75">
-        <v>-6.587000000000003</v>
+        <v>-5.106000000000009</v>
       </c>
       <c r="F75">
-        <v>108.113</v>
+        <v>109.594</v>
       </c>
       <c r="G75">
         <v>3.94</v>
@@ -7559,37 +7559,37 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M75">
-        <v>25.4930454</v>
+        <v>25.8422652</v>
       </c>
       <c r="N75">
-        <v>-15.65637873333333</v>
+        <v>-16.00559853333333</v>
       </c>
       <c r="O75">
-        <v>-2.974711959333333</v>
+        <v>-3.041063721333333</v>
       </c>
       <c r="P75">
-        <v>-12.681666774</v>
+        <v>-12.964534812</v>
       </c>
       <c r="Q75">
-        <v>-8.701666774</v>
+        <v>-8.984534812</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1851761503235315</v>
+        <v>0.1905367714898212</v>
       </c>
       <c r="T75">
-        <v>2.552723140057719</v>
+        <v>2.650904799290709</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.0733128050157031</v>
+        <v>0.0723220914344098</v>
       </c>
       <c r="W75">
-        <v>0.2185128405772972</v>
+        <v>0.2187464508397662</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3858568685037005</v>
+        <v>0.3806425864968938</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7605,22 +7605,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2114119342087805</v>
+        <v>0.2133119342087805</v>
       </c>
       <c r="C76">
-        <v>-70.87450990046891</v>
+        <v>-72.74999541280708</v>
       </c>
       <c r="D76">
-        <v>34.77949009953109</v>
+        <v>34.38500458719291</v>
       </c>
       <c r="E76">
-        <v>-5.106000000000009</v>
+        <v>-3.625000000000014</v>
       </c>
       <c r="F76">
-        <v>109.594</v>
+        <v>111.075</v>
       </c>
       <c r="G76">
         <v>3.94</v>
@@ -7641,37 +7641,37 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M76">
-        <v>25.8422652</v>
+        <v>26.191485</v>
       </c>
       <c r="N76">
-        <v>-16.00559853333333</v>
+        <v>-16.35481833333333</v>
       </c>
       <c r="O76">
-        <v>-3.041063721333333</v>
+        <v>-3.107415483333333</v>
       </c>
       <c r="P76">
-        <v>-12.964534812</v>
+        <v>-13.24740285</v>
       </c>
       <c r="Q76">
-        <v>-8.984534812</v>
+        <v>-9.26740285</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1905367714898212</v>
+        <v>0.1963262423494141</v>
       </c>
       <c r="T76">
-        <v>2.650904799290709</v>
+        <v>2.756940991262338</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.0723220914344098</v>
+        <v>0.07135779688195101</v>
       </c>
       <c r="W76">
-        <v>0.2187464508397662</v>
+        <v>0.218973831495236</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7679,7 +7679,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3806425864968938</v>
+        <v>0.3755673520102685</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7687,22 +7687,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2133119342087805</v>
+        <v>0.2152119342087805</v>
       </c>
       <c r="C77">
-        <v>-72.74999541280708</v>
+        <v>-74.61663240479817</v>
       </c>
       <c r="D77">
-        <v>34.38500458719291</v>
+        <v>33.99936759520183</v>
       </c>
       <c r="E77">
-        <v>-3.625000000000014</v>
+        <v>-2.144000000000005</v>
       </c>
       <c r="F77">
-        <v>111.075</v>
+        <v>112.556</v>
       </c>
       <c r="G77">
         <v>3.94</v>
@@ -7723,37 +7723,37 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M77">
-        <v>26.191485</v>
+        <v>26.5407048</v>
       </c>
       <c r="N77">
-        <v>-16.35481833333333</v>
+        <v>-16.70403813333333</v>
       </c>
       <c r="O77">
-        <v>-3.107415483333333</v>
+        <v>-3.173767245333333</v>
       </c>
       <c r="P77">
-        <v>-13.24740285</v>
+        <v>-13.530270888</v>
       </c>
       <c r="Q77">
-        <v>-9.26740285</v>
+        <v>-9.550270888</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1963262423494141</v>
+        <v>0.202598169113973</v>
       </c>
       <c r="T77">
-        <v>2.756940991262338</v>
+        <v>2.871813532564935</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.07135779688195101</v>
+        <v>0.07041887850192534</v>
       </c>
       <c r="W77">
-        <v>0.218973831495236</v>
+        <v>0.219195228449246</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3755673520102685</v>
+        <v>0.3706256763259228</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7769,22 +7769,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2152119342087805</v>
+        <v>0.2171119342087805</v>
       </c>
       <c r="C78">
-        <v>-74.61663240479817</v>
+        <v>-76.47471529005796</v>
       </c>
       <c r="D78">
-        <v>33.99936759520183</v>
+        <v>33.62228470994203</v>
       </c>
       <c r="E78">
-        <v>-2.144000000000005</v>
+        <v>-0.6630000000000109</v>
       </c>
       <c r="F78">
-        <v>112.556</v>
+        <v>114.037</v>
       </c>
       <c r="G78">
         <v>3.94</v>
@@ -7805,37 +7805,37 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M78">
-        <v>26.5407048</v>
+        <v>26.8899246</v>
       </c>
       <c r="N78">
-        <v>-16.70403813333333</v>
+        <v>-17.05325793333333</v>
       </c>
       <c r="O78">
-        <v>-3.173767245333333</v>
+        <v>-3.240119007333333</v>
       </c>
       <c r="P78">
-        <v>-13.530270888</v>
+        <v>-13.813138926</v>
       </c>
       <c r="Q78">
-        <v>-9.550270888</v>
+        <v>-9.833138926</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.202598169113973</v>
+        <v>0.2094154808145806</v>
       </c>
       <c r="T78">
-        <v>2.871813532564935</v>
+        <v>2.996674990502541</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.07041887850192534</v>
+        <v>0.06950434761228994</v>
       </c>
       <c r="W78">
-        <v>0.219195228449246</v>
+        <v>0.219410874833022</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7843,7 +7843,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3706256763259228</v>
+        <v>0.3658123558541576</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7851,22 +7851,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2171119342087805</v>
+        <v>0.2190119342087805</v>
       </c>
       <c r="C79">
-        <v>-76.47471529005796</v>
+        <v>-78.32452556425011</v>
       </c>
       <c r="D79">
-        <v>33.62228470994203</v>
+        <v>33.25347443574989</v>
       </c>
       <c r="E79">
-        <v>-0.6630000000000109</v>
+        <v>0.8179999999999978</v>
       </c>
       <c r="F79">
-        <v>114.037</v>
+        <v>115.518</v>
       </c>
       <c r="G79">
         <v>3.94</v>
@@ -7887,37 +7887,37 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M79">
-        <v>26.8899246</v>
+        <v>27.2391444</v>
       </c>
       <c r="N79">
-        <v>-17.05325793333333</v>
+        <v>-17.40247773333333</v>
       </c>
       <c r="O79">
-        <v>-3.240119007333333</v>
+        <v>-3.306470769333334</v>
       </c>
       <c r="P79">
-        <v>-13.813138926</v>
+        <v>-14.096006964</v>
       </c>
       <c r="Q79">
-        <v>-9.833138926</v>
+        <v>-10.116006964</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2094154808145806</v>
+        <v>0.2168525481243342</v>
       </c>
       <c r="T79">
-        <v>2.996674990502541</v>
+        <v>3.132887490070838</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.06950434761228994</v>
+        <v>0.0686132662326452</v>
       </c>
       <c r="W79">
-        <v>0.219410874833022</v>
+        <v>0.2196209918223423</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3658123558541576</v>
+        <v>0.3611224538560274</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7933,22 +7933,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2190119342087805</v>
+        <v>0.2209119342087805</v>
       </c>
       <c r="C80">
-        <v>-78.32452556425011</v>
+        <v>-80.16633250589805</v>
       </c>
       <c r="D80">
-        <v>33.25347443574989</v>
+        <v>32.89266749410195</v>
       </c>
       <c r="E80">
-        <v>0.8179999999999978</v>
+        <v>2.298999999999992</v>
       </c>
       <c r="F80">
-        <v>115.518</v>
+        <v>116.999</v>
       </c>
       <c r="G80">
         <v>3.94</v>
@@ -7969,37 +7969,37 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M80">
-        <v>27.2391444</v>
+        <v>27.5883642</v>
       </c>
       <c r="N80">
-        <v>-17.40247773333333</v>
+        <v>-17.75169753333333</v>
       </c>
       <c r="O80">
-        <v>-3.306470769333334</v>
+        <v>-3.372822531333334</v>
       </c>
       <c r="P80">
-        <v>-14.096006964</v>
+        <v>-14.378875002</v>
       </c>
       <c r="Q80">
-        <v>-10.116006964</v>
+        <v>-10.398875002</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2168525481243342</v>
+        <v>0.2249979075588263</v>
       </c>
       <c r="T80">
-        <v>3.132887490070838</v>
+        <v>3.28207260864564</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.0686132662326452</v>
+        <v>0.06774474387526994</v>
       </c>
       <c r="W80">
-        <v>0.2196209918223423</v>
+        <v>0.2198257893942114</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3611224538560274</v>
+        <v>0.3565512835540523</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8015,22 +8015,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2209119342087805</v>
+        <v>0.2228119342087805</v>
       </c>
       <c r="C81">
-        <v>-80.16633250589805</v>
+        <v>-82.0003938320631</v>
       </c>
       <c r="D81">
-        <v>32.89266749410195</v>
+        <v>32.53960616793691</v>
       </c>
       <c r="E81">
-        <v>2.298999999999992</v>
+        <v>3.780000000000001</v>
       </c>
       <c r="F81">
-        <v>116.999</v>
+        <v>118.48</v>
       </c>
       <c r="G81">
         <v>3.94</v>
@@ -8051,37 +8051,37 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M81">
-        <v>27.5883642</v>
+        <v>27.937584</v>
       </c>
       <c r="N81">
-        <v>-17.75169753333333</v>
+        <v>-18.10091733333334</v>
       </c>
       <c r="O81">
-        <v>-3.372822531333334</v>
+        <v>-3.439174293333334</v>
       </c>
       <c r="P81">
-        <v>-14.378875002</v>
+        <v>-14.66174304</v>
       </c>
       <c r="Q81">
-        <v>-10.398875002</v>
+        <v>-10.68174304</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2249979075588263</v>
+        <v>0.2339578029367677</v>
       </c>
       <c r="T81">
-        <v>3.28207260864564</v>
+        <v>3.446176239077923</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.06774474387526994</v>
+        <v>0.06689793457682906</v>
       </c>
       <c r="W81">
-        <v>0.2198257893942114</v>
+        <v>0.2200254670267837</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8089,7 +8089,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3565512835540523</v>
+        <v>0.3520943925096267</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8097,22 +8097,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2228119342087805</v>
+        <v>0.2247119342087805</v>
       </c>
       <c r="C82">
-        <v>-82.0003938320631</v>
+        <v>-83.82695631224362</v>
       </c>
       <c r="D82">
-        <v>32.53960616793691</v>
+        <v>32.19404368775638</v>
       </c>
       <c r="E82">
-        <v>3.780000000000001</v>
+        <v>5.260999999999996</v>
       </c>
       <c r="F82">
-        <v>118.48</v>
+        <v>119.961</v>
       </c>
       <c r="G82">
         <v>3.94</v>
@@ -8133,37 +8133,37 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M82">
-        <v>27.937584</v>
+        <v>28.2868038</v>
       </c>
       <c r="N82">
-        <v>-18.10091733333334</v>
+        <v>-18.45013713333334</v>
       </c>
       <c r="O82">
-        <v>-3.439174293333334</v>
+        <v>-3.505526055333334</v>
       </c>
       <c r="P82">
-        <v>-14.66174304</v>
+        <v>-14.944611078</v>
       </c>
       <c r="Q82">
-        <v>-10.68174304</v>
+        <v>-10.964611078</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2339578029367677</v>
+        <v>0.2438608451965976</v>
       </c>
       <c r="T82">
-        <v>3.446176239077923</v>
+        <v>3.627553935871498</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.06689793457682906</v>
+        <v>0.06607203414995463</v>
       </c>
       <c r="W82">
-        <v>0.2200254670267837</v>
+        <v>0.2202202143474407</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8171,7 +8171,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3520943925096267</v>
+        <v>0.347747548157656</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8179,22 +8179,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2247119342087805</v>
+        <v>0.2266119342087805</v>
       </c>
       <c r="C83">
-        <v>-83.82695631224362</v>
+        <v>-85.64625634356847</v>
       </c>
       <c r="D83">
-        <v>32.19404368775638</v>
+        <v>31.85574365643154</v>
       </c>
       <c r="E83">
-        <v>5.260999999999996</v>
+        <v>6.742000000000004</v>
       </c>
       <c r="F83">
-        <v>119.961</v>
+        <v>121.442</v>
       </c>
       <c r="G83">
         <v>3.94</v>
@@ -8215,37 +8215,37 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M83">
-        <v>28.2868038</v>
+        <v>28.6360236</v>
       </c>
       <c r="N83">
-        <v>-18.45013713333334</v>
+        <v>-18.79935693333334</v>
       </c>
       <c r="O83">
-        <v>-3.505526055333334</v>
+        <v>-3.571877817333334</v>
       </c>
       <c r="P83">
-        <v>-14.944611078</v>
+        <v>-15.227479116</v>
       </c>
       <c r="Q83">
-        <v>-10.964611078</v>
+        <v>-11.247479116</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2438608451965976</v>
+        <v>0.2548642254852974</v>
       </c>
       <c r="T83">
-        <v>3.627553935871498</v>
+        <v>3.829084710086581</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.06607203414995463</v>
+        <v>0.06526627763593079</v>
       </c>
       <c r="W83">
-        <v>0.2202202143474407</v>
+        <v>0.2204102117334475</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.347747548157656</v>
+        <v>0.3435067243996358</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8261,22 +8261,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2266119342087805</v>
+        <v>0.2285119342087805</v>
       </c>
       <c r="C84">
-        <v>-85.64625634356847</v>
+        <v>-87.45852049010232</v>
       </c>
       <c r="D84">
-        <v>31.85574365643154</v>
+        <v>31.52447950989769</v>
       </c>
       <c r="E84">
-        <v>6.742000000000004</v>
+        <v>8.222999999999999</v>
       </c>
       <c r="F84">
-        <v>121.442</v>
+        <v>122.923</v>
       </c>
       <c r="G84">
         <v>3.94</v>
@@ -8297,37 +8297,37 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M84">
-        <v>28.6360236</v>
+        <v>28.9852434</v>
       </c>
       <c r="N84">
-        <v>-18.79935693333334</v>
+        <v>-19.14857673333334</v>
       </c>
       <c r="O84">
-        <v>-3.571877817333334</v>
+        <v>-3.638229579333334</v>
       </c>
       <c r="P84">
-        <v>-15.227479116</v>
+        <v>-15.510347154</v>
       </c>
       <c r="Q84">
-        <v>-11.247479116</v>
+        <v>-11.530347154</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2548642254852974</v>
+        <v>0.2671621211020796</v>
       </c>
       <c r="T84">
-        <v>3.829084710086581</v>
+        <v>4.054324987150498</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.06526627763593079</v>
+        <v>0.06447993694152199</v>
       </c>
       <c r="W84">
-        <v>0.2204102117334475</v>
+        <v>0.2205956308691891</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3435067243996358</v>
+        <v>0.3393680891659052</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8343,22 +8343,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2285119342087805</v>
+        <v>0.2304119342087805</v>
       </c>
       <c r="C85">
-        <v>-87.45852049010232</v>
+        <v>-89.26396598884818</v>
       </c>
       <c r="D85">
-        <v>31.52447950989769</v>
+        <v>31.20003401115183</v>
       </c>
       <c r="E85">
-        <v>8.222999999999999</v>
+        <v>9.704000000000008</v>
       </c>
       <c r="F85">
-        <v>122.923</v>
+        <v>124.404</v>
       </c>
       <c r="G85">
         <v>3.94</v>
@@ -8379,37 +8379,37 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M85">
-        <v>28.9852434</v>
+        <v>29.33446320000001</v>
       </c>
       <c r="N85">
-        <v>-19.14857673333334</v>
+        <v>-19.49779653333334</v>
       </c>
       <c r="O85">
-        <v>-3.638229579333334</v>
+        <v>-3.704581341333335</v>
       </c>
       <c r="P85">
-        <v>-15.510347154</v>
+        <v>-15.79321519200001</v>
       </c>
       <c r="Q85">
-        <v>-11.530347154</v>
+        <v>-11.813215192</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2671621211020796</v>
+        <v>0.2809972536709597</v>
       </c>
       <c r="T85">
-        <v>4.054324987150498</v>
+        <v>4.307720298847405</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.06447993694152199</v>
+        <v>0.0637123186445991</v>
       </c>
       <c r="W85">
-        <v>0.2205956308691891</v>
+        <v>0.2207766352636035</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8417,7 +8417,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3393680891659052</v>
+        <v>0.3353279928663111</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8425,22 +8425,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2304119342087805</v>
+        <v>0.2323119342087805</v>
       </c>
       <c r="C86">
-        <v>-89.26396598884817</v>
+        <v>-91.06280122482201</v>
       </c>
       <c r="D86">
-        <v>31.20003401115183</v>
+        <v>30.88219877517797</v>
       </c>
       <c r="E86">
-        <v>9.703999999999994</v>
+        <v>11.18499999999999</v>
       </c>
       <c r="F86">
-        <v>124.404</v>
+        <v>125.885</v>
       </c>
       <c r="G86">
         <v>3.94</v>
@@ -8461,37 +8461,37 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M86">
-        <v>29.3344632</v>
+        <v>29.683683</v>
       </c>
       <c r="N86">
-        <v>-19.49779653333334</v>
+        <v>-19.84701633333333</v>
       </c>
       <c r="O86">
-        <v>-3.704581341333334</v>
+        <v>-3.770933103333333</v>
       </c>
       <c r="P86">
-        <v>-15.793215192</v>
+        <v>-16.07608323</v>
       </c>
       <c r="Q86">
-        <v>-11.813215192</v>
+        <v>-12.09608323</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2809972536709595</v>
+        <v>0.2966770705823568</v>
       </c>
       <c r="T86">
-        <v>4.307720298847402</v>
+        <v>4.594901652103895</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.06371231864459911</v>
+        <v>0.06296276195466266</v>
       </c>
       <c r="W86">
-        <v>0.2207766352636035</v>
+        <v>0.2209533807310906</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3353279928663111</v>
+        <v>0.3313829576561192</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8507,22 +8507,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2323119342087805</v>
+        <v>0.2342119342087805</v>
       </c>
       <c r="C87">
-        <v>-91.06280122482201</v>
+        <v>-92.85522617738275</v>
       </c>
       <c r="D87">
-        <v>30.88219877517797</v>
+        <v>30.57077382261726</v>
       </c>
       <c r="E87">
-        <v>11.18499999999999</v>
+        <v>12.666</v>
       </c>
       <c r="F87">
-        <v>125.885</v>
+        <v>127.366</v>
       </c>
       <c r="G87">
         <v>3.94</v>
@@ -8543,37 +8543,37 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M87">
-        <v>29.683683</v>
+        <v>30.0329028</v>
       </c>
       <c r="N87">
-        <v>-19.84701633333333</v>
+        <v>-20.19623613333334</v>
       </c>
       <c r="O87">
-        <v>-3.770933103333333</v>
+        <v>-3.837284865333334</v>
       </c>
       <c r="P87">
-        <v>-16.07608323</v>
+        <v>-16.358951268</v>
       </c>
       <c r="Q87">
-        <v>-12.09608323</v>
+        <v>-12.378951268</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2966770705823568</v>
+        <v>0.3145968613382394</v>
       </c>
       <c r="T87">
-        <v>4.594901652103895</v>
+        <v>4.92310891296846</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.06296276195466266</v>
+        <v>0.06223063681565494</v>
       </c>
       <c r="W87">
-        <v>0.2209533807310906</v>
+        <v>0.2211260158388686</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3313829576561192</v>
+        <v>0.3275296674508155</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8589,22 +8589,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2342119342087805</v>
+        <v>0.2361119342087805</v>
       </c>
       <c r="C88">
-        <v>-92.85522617738275</v>
+        <v>-94.64143283982594</v>
       </c>
       <c r="D88">
-        <v>30.57077382261726</v>
+        <v>30.26556716017407</v>
       </c>
       <c r="E88">
-        <v>12.666</v>
+        <v>14.14700000000001</v>
       </c>
       <c r="F88">
-        <v>127.366</v>
+        <v>128.847</v>
       </c>
       <c r="G88">
         <v>3.94</v>
@@ -8625,37 +8625,37 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M88">
-        <v>30.0329028</v>
+        <v>30.3821226</v>
       </c>
       <c r="N88">
-        <v>-20.19623613333334</v>
+        <v>-20.54545593333334</v>
       </c>
       <c r="O88">
-        <v>-3.837284865333334</v>
+        <v>-3.903636627333334</v>
       </c>
       <c r="P88">
-        <v>-16.358951268</v>
+        <v>-16.641819306</v>
       </c>
       <c r="Q88">
-        <v>-12.378951268</v>
+        <v>-12.661819306</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3145968613382394</v>
+        <v>0.3352735429796425</v>
       </c>
       <c r="T88">
-        <v>4.92310891296846</v>
+        <v>5.301809598581418</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.06223063681565494</v>
+        <v>0.06151534213961293</v>
       </c>
       <c r="W88">
-        <v>0.2211260158388686</v>
+        <v>0.2212946823234793</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3275296674508155</v>
+        <v>0.3237649586295417</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8671,22 +8671,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2361119342087805</v>
+        <v>0.2380119342087805</v>
       </c>
       <c r="C89">
-        <v>-94.64143283982594</v>
+        <v>-96.42160561409223</v>
       </c>
       <c r="D89">
-        <v>30.26556716017407</v>
+        <v>29.96639438590778</v>
       </c>
       <c r="E89">
-        <v>14.14700000000001</v>
+        <v>15.628</v>
       </c>
       <c r="F89">
-        <v>128.847</v>
+        <v>130.328</v>
       </c>
       <c r="G89">
         <v>3.94</v>
@@ -8707,37 +8707,37 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M89">
-        <v>30.3821226</v>
+        <v>30.7313424</v>
       </c>
       <c r="N89">
-        <v>-20.54545593333334</v>
+        <v>-20.89467573333334</v>
       </c>
       <c r="O89">
-        <v>-3.903636627333334</v>
+        <v>-3.969988389333334</v>
       </c>
       <c r="P89">
-        <v>-16.641819306</v>
+        <v>-16.924687344</v>
       </c>
       <c r="Q89">
-        <v>-12.661819306</v>
+        <v>-12.944687344</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3352735429796425</v>
+        <v>0.3593963382279461</v>
       </c>
       <c r="T89">
-        <v>5.301809598581418</v>
+        <v>5.74362706512987</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.06151534213961293</v>
+        <v>0.06081630416075369</v>
       </c>
       <c r="W89">
-        <v>0.2212946823234793</v>
+        <v>0.2214595154788943</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3237649586295417</v>
+        <v>0.3200858113723879</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8753,22 +8753,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2380119342087805</v>
+        <v>0.2399119342087805</v>
       </c>
       <c r="C90">
-        <v>-96.42160561409223</v>
+        <v>-98.19592168229433</v>
       </c>
       <c r="D90">
-        <v>29.96639438590778</v>
+        <v>29.67307831770567</v>
       </c>
       <c r="E90">
-        <v>15.628</v>
+        <v>17.10899999999999</v>
       </c>
       <c r="F90">
-        <v>130.328</v>
+        <v>131.809</v>
       </c>
       <c r="G90">
         <v>3.94</v>
@@ -8789,37 +8789,37 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M90">
-        <v>30.7313424</v>
+        <v>31.0805622</v>
       </c>
       <c r="N90">
-        <v>-20.89467573333334</v>
+        <v>-21.24389553333333</v>
       </c>
       <c r="O90">
-        <v>-3.969988389333334</v>
+        <v>-4.036340151333333</v>
       </c>
       <c r="P90">
-        <v>-16.924687344</v>
+        <v>-17.207555382</v>
       </c>
       <c r="Q90">
-        <v>-12.944687344</v>
+        <v>-13.227555382</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3593963382279461</v>
+        <v>0.3879050962486684</v>
       </c>
       <c r="T90">
-        <v>5.74362706512987</v>
+        <v>6.265774980141677</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.06081630416075369</v>
+        <v>0.06013297490052051</v>
       </c>
       <c r="W90">
-        <v>0.2214595154788943</v>
+        <v>0.2216206445184573</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3200858113723879</v>
+        <v>0.316489341581687</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8835,22 +8835,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2399119342087805</v>
+        <v>0.2418119342087805</v>
       </c>
       <c r="C91">
-        <v>-98.19592168229433</v>
+        <v>-99.96455135663643</v>
       </c>
       <c r="D91">
-        <v>29.67307831770567</v>
+        <v>29.38544864336355</v>
       </c>
       <c r="E91">
-        <v>17.10899999999999</v>
+        <v>18.58999999999999</v>
       </c>
       <c r="F91">
-        <v>131.809</v>
+        <v>133.29</v>
       </c>
       <c r="G91">
         <v>3.94</v>
@@ -8871,37 +8871,37 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M91">
-        <v>31.0805622</v>
+        <v>31.429782</v>
       </c>
       <c r="N91">
-        <v>-21.24389553333333</v>
+        <v>-21.59311533333333</v>
       </c>
       <c r="O91">
-        <v>-4.036340151333333</v>
+        <v>-4.102691913333333</v>
       </c>
       <c r="P91">
-        <v>-17.207555382</v>
+        <v>-17.49042342</v>
       </c>
       <c r="Q91">
-        <v>-13.227555382</v>
+        <v>-13.51042342</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3879050962486684</v>
+        <v>0.4221156058735352</v>
       </c>
       <c r="T91">
-        <v>6.265774980141677</v>
+        <v>6.892352478155845</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.06013297490052051</v>
+        <v>0.05946483073495917</v>
       </c>
       <c r="W91">
-        <v>0.2216206445184573</v>
+        <v>0.2217781929126966</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.316489341581687</v>
+        <v>0.3129727933418904</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8917,22 +8917,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2418119342087805</v>
+        <v>0.2437119342087805</v>
       </c>
       <c r="C92">
-        <v>-99.96455135663643</v>
+        <v>-101.7276584091778</v>
       </c>
       <c r="D92">
-        <v>29.38544864336355</v>
+        <v>29.10334159082223</v>
       </c>
       <c r="E92">
-        <v>18.58999999999999</v>
+        <v>20.07099999999998</v>
       </c>
       <c r="F92">
-        <v>133.29</v>
+        <v>134.771</v>
       </c>
       <c r="G92">
         <v>3.94</v>
@@ -8953,37 +8953,37 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M92">
-        <v>31.429782</v>
+        <v>31.7790018</v>
       </c>
       <c r="N92">
-        <v>-21.59311533333333</v>
+        <v>-21.94233513333333</v>
       </c>
       <c r="O92">
-        <v>-4.102691913333333</v>
+        <v>-4.169043675333334</v>
       </c>
       <c r="P92">
-        <v>-17.49042342</v>
+        <v>-17.773291458</v>
       </c>
       <c r="Q92">
-        <v>-13.51042342</v>
+        <v>-13.793291458</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4221156058735352</v>
+        <v>0.4639284509705948</v>
       </c>
       <c r="T92">
-        <v>6.892352478155845</v>
+        <v>7.658169420173162</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.05946483073495917</v>
+        <v>0.05881137105655303</v>
       </c>
       <c r="W92">
-        <v>0.2217781929126966</v>
+        <v>0.2219322787048648</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8991,7 +8991,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3129727933418904</v>
+        <v>0.3095335318765949</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8999,22 +8999,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2437119342087805</v>
+        <v>0.2456119342087805</v>
       </c>
       <c r="C93">
-        <v>-101.7276584091778</v>
+        <v>-103.4854003827817</v>
       </c>
       <c r="D93">
-        <v>29.10334159082223</v>
+        <v>28.82659961721827</v>
       </c>
       <c r="E93">
-        <v>20.07099999999998</v>
+        <v>21.55200000000001</v>
       </c>
       <c r="F93">
-        <v>134.771</v>
+        <v>136.252</v>
       </c>
       <c r="G93">
         <v>3.94</v>
@@ -9035,37 +9035,37 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M93">
-        <v>31.7790018</v>
+        <v>32.1282216</v>
       </c>
       <c r="N93">
-        <v>-21.94233513333333</v>
+        <v>-22.29155493333334</v>
       </c>
       <c r="O93">
-        <v>-4.169043675333334</v>
+        <v>-4.235395437333334</v>
       </c>
       <c r="P93">
-        <v>-17.773291458</v>
+        <v>-18.056159496</v>
       </c>
       <c r="Q93">
-        <v>-13.793291458</v>
+        <v>-14.076159496</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4639284509705948</v>
+        <v>0.5161945073419193</v>
       </c>
       <c r="T93">
-        <v>7.658169420173162</v>
+        <v>8.615440597694811</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.05881137105655303</v>
+        <v>0.05817211702332962</v>
       </c>
       <c r="W93">
-        <v>0.2219322787048648</v>
+        <v>0.2220830148058989</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9073,7 +9073,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3095335318765949</v>
+        <v>0.3061690369648927</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9081,22 +9081,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2456119342087805</v>
+        <v>0.2475119342087805</v>
       </c>
       <c r="C94">
-        <v>-103.4854003827817</v>
+        <v>-105.2379288844916</v>
       </c>
       <c r="D94">
-        <v>28.82659961721827</v>
+        <v>28.55507111550839</v>
       </c>
       <c r="E94">
-        <v>21.55200000000001</v>
+        <v>23.033</v>
       </c>
       <c r="F94">
-        <v>136.252</v>
+        <v>137.733</v>
       </c>
       <c r="G94">
         <v>3.94</v>
@@ -9117,37 +9117,37 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M94">
-        <v>32.1282216</v>
+        <v>32.4774414</v>
       </c>
       <c r="N94">
-        <v>-22.29155493333334</v>
+        <v>-22.64077473333334</v>
       </c>
       <c r="O94">
-        <v>-4.235395437333334</v>
+        <v>-4.301747199333334</v>
       </c>
       <c r="P94">
-        <v>-18.056159496</v>
+        <v>-18.339027534</v>
       </c>
       <c r="Q94">
-        <v>-14.076159496</v>
+        <v>-14.359027534</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5161945073419193</v>
+        <v>0.5833937226764793</v>
       </c>
       <c r="T94">
-        <v>8.615440597694811</v>
+        <v>9.846217825936927</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.05817211702332962</v>
+        <v>0.05754661038867016</v>
       </c>
       <c r="W94">
-        <v>0.2220830148058989</v>
+        <v>0.2222305092703516</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9155,7 +9155,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3061690369648927</v>
+        <v>0.3028768967824745</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9163,22 +9163,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2475119342087805</v>
+        <v>0.2494119342087805</v>
       </c>
       <c r="C95">
-        <v>-105.2379288844916</v>
+        <v>-106.9853898624804</v>
       </c>
       <c r="D95">
-        <v>28.55507111550839</v>
+        <v>28.28861013751956</v>
       </c>
       <c r="E95">
-        <v>23.033</v>
+        <v>24.514</v>
       </c>
       <c r="F95">
-        <v>137.733</v>
+        <v>139.214</v>
       </c>
       <c r="G95">
         <v>3.94</v>
@@ -9199,37 +9199,37 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M95">
-        <v>32.4774414</v>
+        <v>32.8266612</v>
       </c>
       <c r="N95">
-        <v>-22.64077473333334</v>
+        <v>-22.98999453333334</v>
       </c>
       <c r="O95">
-        <v>-4.301747199333334</v>
+        <v>-4.368098961333335</v>
       </c>
       <c r="P95">
-        <v>-18.339027534</v>
+        <v>-18.621895572</v>
       </c>
       <c r="Q95">
-        <v>-14.359027534</v>
+        <v>-14.641895572</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5833937226764793</v>
+        <v>0.6729926764558926</v>
       </c>
       <c r="T95">
-        <v>9.846217825936927</v>
+        <v>11.48725413025975</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.05754661038867016</v>
+        <v>0.05693441240581196</v>
       </c>
       <c r="W95">
-        <v>0.2222305092703516</v>
+        <v>0.2223748655547095</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3028768967824745</v>
+        <v>0.2996548021358525</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9245,22 +9245,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2494119342087805</v>
+        <v>0.2513119342087805</v>
       </c>
       <c r="C96">
-        <v>-106.9853898624804</v>
+        <v>-108.7279238676379</v>
       </c>
       <c r="D96">
-        <v>28.28861013751956</v>
+        <v>28.02707613236207</v>
       </c>
       <c r="E96">
-        <v>24.514</v>
+        <v>25.99499999999999</v>
       </c>
       <c r="F96">
-        <v>139.214</v>
+        <v>140.695</v>
       </c>
       <c r="G96">
         <v>3.94</v>
@@ -9281,37 +9281,37 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M96">
-        <v>32.8266612</v>
+        <v>33.175881</v>
       </c>
       <c r="N96">
-        <v>-22.98999453333334</v>
+        <v>-23.33921433333333</v>
       </c>
       <c r="O96">
-        <v>-4.368098961333335</v>
+        <v>-4.434450723333333</v>
       </c>
       <c r="P96">
-        <v>-18.621895572</v>
+        <v>-18.90476361</v>
       </c>
       <c r="Q96">
-        <v>-14.641895572</v>
+        <v>-14.92476361</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6729926764558926</v>
+        <v>0.7984312117470714</v>
       </c>
       <c r="T96">
-        <v>11.48725413025975</v>
+        <v>13.78470495631171</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.05693441240581196</v>
+        <v>0.05633510280154027</v>
       </c>
       <c r="W96">
-        <v>0.2223748655547095</v>
+        <v>0.2225161827593968</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2996548021358525</v>
+        <v>0.2965005410607383</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9327,22 +9327,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2513119342087805</v>
+        <v>0.2532119342087805</v>
       </c>
       <c r="C97">
-        <v>-108.7279238676379</v>
+        <v>-110.4656663007801</v>
       </c>
       <c r="D97">
-        <v>28.02707613236207</v>
+        <v>27.77033369921989</v>
       </c>
       <c r="E97">
-        <v>25.99499999999999</v>
+        <v>27.47600000000001</v>
       </c>
       <c r="F97">
-        <v>140.695</v>
+        <v>142.176</v>
       </c>
       <c r="G97">
         <v>3.94</v>
@@ -9363,37 +9363,37 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M97">
-        <v>33.175881</v>
+        <v>33.5251008</v>
       </c>
       <c r="N97">
-        <v>-23.33921433333333</v>
+        <v>-23.68843413333334</v>
       </c>
       <c r="O97">
-        <v>-4.434450723333333</v>
+        <v>-4.500802485333335</v>
       </c>
       <c r="P97">
-        <v>-18.90476361</v>
+        <v>-19.187631648</v>
       </c>
       <c r="Q97">
-        <v>-14.92476361</v>
+        <v>-15.207631648</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7984312117470714</v>
+        <v>0.9865890146838399</v>
       </c>
       <c r="T97">
-        <v>13.78470495631171</v>
+        <v>17.23088119538964</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.05633510280154027</v>
+        <v>0.05574827881402421</v>
       </c>
       <c r="W97">
-        <v>0.2225161827593968</v>
+        <v>0.2226545558556531</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2965005410607383</v>
+        <v>0.2934119937580222</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9409,22 +9409,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2532119342087805</v>
+        <v>0.2551119342087805</v>
       </c>
       <c r="C98">
-        <v>-110.4656663007801</v>
+        <v>-112.1987476463946</v>
       </c>
       <c r="D98">
-        <v>27.77033369921989</v>
+        <v>27.51825235360542</v>
       </c>
       <c r="E98">
-        <v>27.47599999999998</v>
+        <v>28.95699999999998</v>
       </c>
       <c r="F98">
-        <v>142.176</v>
+        <v>143.657</v>
       </c>
       <c r="G98">
         <v>3.94</v>
@@ -9445,37 +9445,37 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M98">
-        <v>33.5251008</v>
+        <v>33.8743206</v>
       </c>
       <c r="N98">
-        <v>-23.68843413333333</v>
+        <v>-24.03765393333333</v>
       </c>
       <c r="O98">
-        <v>-4.500802485333333</v>
+        <v>-4.567154247333333</v>
       </c>
       <c r="P98">
-        <v>-19.187631648</v>
+        <v>-19.470499686</v>
       </c>
       <c r="Q98">
-        <v>-15.207631648</v>
+        <v>-15.490499686</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9865890146838371</v>
+        <v>1.300185352911783</v>
       </c>
       <c r="T98">
-        <v>17.23088119538959</v>
+        <v>22.97450826051946</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.05574827881402423</v>
+        <v>0.05517355429016831</v>
       </c>
       <c r="W98">
-        <v>0.2226545558556531</v>
+        <v>0.2227900758983783</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9483,7 +9483,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2934119937580223</v>
+        <v>0.2903871278429911</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9491,22 +9491,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2551119342087805</v>
+        <v>0.2570119342087805</v>
       </c>
       <c r="C99">
-        <v>-112.1987476463946</v>
+        <v>-113.9272936937698</v>
       </c>
       <c r="D99">
-        <v>27.51825235360542</v>
+        <v>27.27070630623024</v>
       </c>
       <c r="E99">
-        <v>28.95699999999998</v>
+        <v>30.438</v>
       </c>
       <c r="F99">
-        <v>143.657</v>
+        <v>145.138</v>
       </c>
       <c r="G99">
         <v>3.94</v>
@@ -9527,37 +9527,37 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M99">
-        <v>33.8743206</v>
+        <v>34.2235404</v>
       </c>
       <c r="N99">
-        <v>-24.03765393333333</v>
+        <v>-24.38687373333334</v>
       </c>
       <c r="O99">
-        <v>-4.567154247333333</v>
+        <v>-4.633506009333335</v>
       </c>
       <c r="P99">
-        <v>-19.470499686</v>
+        <v>-19.753367724</v>
       </c>
       <c r="Q99">
-        <v>-15.490499686</v>
+        <v>-15.773367724</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.300185352911783</v>
+        <v>1.927378029367674</v>
       </c>
       <c r="T99">
-        <v>22.97450826051946</v>
+        <v>34.46176239077919</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.05517355429016831</v>
+        <v>0.05461055883822781</v>
       </c>
       <c r="W99">
-        <v>0.2227900758983783</v>
+        <v>0.2229228302259459</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9565,7 +9565,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2903871278429911</v>
+        <v>0.2874239938854095</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9573,22 +9573,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2570119342087805</v>
+        <v>0.2589119342087805</v>
       </c>
       <c r="C100">
-        <v>-113.9272936937698</v>
+        <v>-115.6514257462952</v>
       </c>
       <c r="D100">
-        <v>27.27070630623024</v>
+        <v>27.02757425370484</v>
       </c>
       <c r="E100">
-        <v>30.438</v>
+        <v>31.919</v>
       </c>
       <c r="F100">
-        <v>145.138</v>
+        <v>146.619</v>
       </c>
       <c r="G100">
         <v>3.94</v>
@@ -9609,37 +9609,37 @@
         <v>9.836666666666666</v>
       </c>
       <c r="M100">
-        <v>34.2235404</v>
+        <v>34.5727602</v>
       </c>
       <c r="N100">
-        <v>-24.38687373333334</v>
+        <v>-24.73609353333334</v>
       </c>
       <c r="O100">
-        <v>-4.633506009333335</v>
+        <v>-4.699857771333335</v>
       </c>
       <c r="P100">
-        <v>-19.753367724</v>
+        <v>-20.036235762</v>
       </c>
       <c r="Q100">
-        <v>-15.773367724</v>
+        <v>-16.056235762</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.927378029367674</v>
+        <v>3.808956058735348</v>
       </c>
       <c r="T100">
-        <v>34.46176239077919</v>
+        <v>68.92352478155837</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.05461055883822781</v>
+        <v>0.05405893703178106</v>
       </c>
       <c r="W100">
-        <v>0.2229228302259459</v>
+        <v>0.223052902647906</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9647,91 +9647,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2874239938854095</v>
+        <v>0.2845207212199004</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2589119342087805</v>
-      </c>
-      <c r="C101">
-        <v>-115.6514257462952</v>
-      </c>
-      <c r="D101">
-        <v>27.02757425370484</v>
-      </c>
-      <c r="E101">
-        <v>31.919</v>
-      </c>
-      <c r="F101">
-        <v>146.619</v>
-      </c>
-      <c r="G101">
-        <v>3.94</v>
-      </c>
-      <c r="H101">
-        <v>33.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>13.81666666666667</v>
-      </c>
-      <c r="K101">
-        <v>3.98</v>
-      </c>
-      <c r="L101">
-        <v>9.836666666666666</v>
-      </c>
-      <c r="M101">
-        <v>34.5727602</v>
-      </c>
-      <c r="N101">
-        <v>-24.73609353333334</v>
-      </c>
-      <c r="O101">
-        <v>-4.699857771333335</v>
-      </c>
-      <c r="P101">
-        <v>-20.036235762</v>
-      </c>
-      <c r="Q101">
-        <v>-16.056235762</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.808956058735348</v>
-      </c>
-      <c r="T101">
-        <v>68.92352478155837</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.05405893703178106</v>
-      </c>
-      <c r="W101">
-        <v>0.223052902647906</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2845207212199004</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
